--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -868,7 +868,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 31/07/2026 09:47 h</t>
+          <t>Shopify daily average | Actualizado: 31/07/2026 12:25 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1122,7 +1122,7 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="7" ht="12" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            ES</t>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="12" customHeight="1">
+    <row r="8" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A8" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="Q8" s="27" t="n"/>
     </row>
-    <row r="9" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="9" ht="12" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            FR</t>
@@ -1328,7 +1328,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="12" customHeight="1">
+    <row r="10" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A10" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Q10" s="27" t="n"/>
     </row>
-    <row r="11" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="11" ht="12" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            DE</t>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="12" customHeight="1">
+    <row r="12" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A12" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Q12" s="27" t="n"/>
     </row>
-    <row r="13" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="13" ht="12" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            IT</t>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="12" customHeight="1">
+    <row r="14" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Q14" s="27" t="n"/>
     </row>
-    <row r="15" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="15" ht="12" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            AT</t>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="12" customHeight="1">
+    <row r="16" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="Q16" s="27" t="n"/>
     </row>
-    <row r="17" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="17" ht="12" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            BE</t>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="12" customHeight="1">
+    <row r="18" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="Q18" s="27" t="n"/>
     </row>
-    <row r="19" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="19" ht="12" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            NL</t>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="12" customHeight="1">
+    <row r="20" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A20" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Q20" s="27" t="n"/>
     </row>
-    <row r="21" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="21" ht="12" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            PT</t>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="12" customHeight="1">
+    <row r="22" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A22" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q22" s="27" t="n"/>
     </row>
-    <row r="23" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="23" ht="12" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            CZ</t>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="12" customHeight="1">
+    <row r="24" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A24" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="Q24" s="27" t="n"/>
     </row>
-    <row r="25" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="25" ht="12" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            DK</t>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="12" customHeight="1">
+    <row r="26" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A26" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="Q26" s="27" t="n"/>
     </row>
-    <row r="27" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="27" ht="12" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            IE</t>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="12" customHeight="1">
+    <row r="28" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A28" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="Q28" s="27" t="n"/>
     </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="29" ht="12" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            LU</t>
@@ -2688,7 +2688,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="12" customHeight="1">
+    <row r="30" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="Q30" s="27" t="n"/>
     </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+    <row r="31" ht="12" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            PL</t>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="12" customHeight="1">
+    <row r="32" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Q32" s="27" t="n"/>
     </row>
-    <row r="33" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="33" ht="12" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">            SE</t>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="12" customHeight="1">
+    <row r="34" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
       <c r="A34" s="26" t="inlineStr">
         <is>
           <t>avg/day</t>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31T07:47:51Z</t>
+          <t>2026-07-31T10:25:14Z</t>
         </is>
       </c>
     </row>
@@ -22550,7 +22550,7 @@
         </is>
       </c>
       <c r="E67" s="50" t="n">
-        <v>4046.54</v>
+        <v>4128.32</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="50" t="n">
-        <v>4046.54</v>
+        <v>4128.32</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         </is>
       </c>
       <c r="E71" s="50" t="n">
-        <v>63672.62</v>
+        <v>64027.01</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="50" t="n">
-        <v>63672.62</v>
+        <v>64027.01</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -22790,7 +22790,7 @@
         </is>
       </c>
       <c r="E72" s="50" t="n">
-        <v>29243.18</v>
+        <v>29481.73</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="50" t="n">
-        <v>29243.18</v>
+        <v>29481.73</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         </is>
       </c>
       <c r="E74" s="50" t="n">
-        <v>16694.29</v>
+        <v>16704.91</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>1</v>
       </c>
       <c r="I74" s="50" t="n">
-        <v>16694.29</v>
+        <v>16704.91</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         </is>
       </c>
       <c r="E79" s="50" t="n">
-        <v>2589.67</v>
+        <v>2401.98</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>1</v>
       </c>
       <c r="I79" s="50" t="n">
-        <v>2589.67</v>
+        <v>2401.98</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>

--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -868,7 +868,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 31/07/2026 12:25 h</t>
+          <t>Shopify daily average | Actualizado: 10/08/2026 23:59 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="D16" s="50" t="n">
-        <v>1150.68</v>
+        <v>1189.65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="50" t="n">
-        <v>1150.68</v>
+        <v>1189.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         </is>
       </c>
       <c r="D17" s="50" t="n">
-        <v>3052.63</v>
+        <v>3139.54</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -10549,9 +10549,173 @@
         <v>1</v>
       </c>
       <c r="H17" s="50" t="n">
-        <v>3052.63</v>
+        <v>3139.54</v>
       </c>
       <c r="I17" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="12" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PAYPAL</t>
+        </is>
+      </c>
+      <c r="D18" s="50" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="n">
+        <v>0.04123371</v>
+      </c>
+      <c r="H18" s="50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="12" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PAYPAL</t>
+        </is>
+      </c>
+      <c r="D19" s="50" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="50" t="n">
+        <v>473.25</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="12" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SHOPIFY</t>
+        </is>
+      </c>
+      <c r="D20" s="50" t="n">
+        <v>1193.23</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="50" t="n">
+        <v>1193.23</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SHOPIFY</t>
+        </is>
+      </c>
+      <c r="D21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SEK</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="n">
+        <v>0.09119511</v>
+      </c>
+      <c r="H21" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>payment_fee_monthly_summary</t>
         </is>
@@ -10571,7 +10735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11295,7 +11459,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11309,10 +11473,10 @@
         </is>
       </c>
       <c r="E23" s="51" t="n">
-        <v>0.85715</v>
+        <v>0.85573</v>
       </c>
       <c r="F23" s="51" t="n">
-        <v>1.16665694</v>
+        <v>1.1685929</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -11328,7 +11492,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11342,10 +11506,10 @@
         </is>
       </c>
       <c r="E24" s="51" t="n">
-        <v>1.1476</v>
+        <v>1.1485</v>
       </c>
       <c r="F24" s="51" t="n">
-        <v>0.87138376</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -11361,12 +11525,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>CZK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -11375,14 +11539,14 @@
         </is>
       </c>
       <c r="E25" s="51" t="n">
-        <v>0.85715</v>
+        <v>24.252</v>
       </c>
       <c r="F25" s="51" t="n">
-        <v>1.16665694</v>
+        <v>0.04123371</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202608)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11558,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11408,26 +11572,26 @@
         </is>
       </c>
       <c r="E26" s="51" t="n">
-        <v>1.1476</v>
+        <v>1</v>
       </c>
       <c r="F26" s="51" t="n">
-        <v>0.87138376</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202608)</t>
+          <t>identity</t>
         </is>
       </c>
     </row>
     <row r="27" ht="12" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11441,31 +11605,31 @@
         </is>
       </c>
       <c r="E27" s="51" t="n">
-        <v>0.85715</v>
+        <v>0.85565</v>
       </c>
       <c r="F27" s="51" t="n">
-        <v>1.16665694</v>
+        <v>1.16870216</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="28" ht="12" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>202609</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11474,31 +11638,31 @@
         </is>
       </c>
       <c r="E28" s="51" t="n">
-        <v>1.1476</v>
+        <v>10.9655</v>
       </c>
       <c r="F28" s="51" t="n">
-        <v>0.87138376</v>
+        <v>0.09119511</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="29" ht="12" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11507,31 +11671,31 @@
         </is>
       </c>
       <c r="E29" s="51" t="n">
-        <v>0.85715</v>
+        <v>1.1555</v>
       </c>
       <c r="F29" s="51" t="n">
-        <v>1.16665694</v>
+        <v>0.86542622</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="30" ht="12" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11540,31 +11704,31 @@
         </is>
       </c>
       <c r="E30" s="51" t="n">
-        <v>1.1476</v>
+        <v>0.85565</v>
       </c>
       <c r="F30" s="51" t="n">
-        <v>0.87138376</v>
+        <v>1.16870216</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="12" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11573,31 +11737,31 @@
         </is>
       </c>
       <c r="E31" s="51" t="n">
-        <v>0.85715</v>
+        <v>1.1555</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>1.16665694</v>
+        <v>0.86542622</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="12" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11606,31 +11770,31 @@
         </is>
       </c>
       <c r="E32" s="51" t="n">
-        <v>1.1476</v>
+        <v>0.85565</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>0.87138376</v>
+        <v>1.16870216</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>202612</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11639,45 +11803,144 @@
         </is>
       </c>
       <c r="E33" s="51" t="n">
-        <v>0.85715</v>
+        <v>1.1555</v>
       </c>
       <c r="F33" s="51" t="n">
-        <v>1.16665694</v>
+        <v>0.86542622</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
+          <t>202611</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E34" s="51" t="n">
+        <v>0.85565</v>
+      </c>
+      <c r="F34" s="51" t="n">
+        <v>1.16870216</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="12" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>202611</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E35" s="51" t="n">
+        <v>1.1555</v>
+      </c>
+      <c r="F35" s="51" t="n">
+        <v>0.86542622</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="12" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>202612</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E36" s="51" t="n">
+        <v>0.85565</v>
+      </c>
+      <c r="F36" s="51" t="n">
+        <v>1.16870216</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="12" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E34" s="51" t="n">
-        <v>1.1476</v>
-      </c>
-      <c r="F34" s="51" t="n">
-        <v>0.87138376</v>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="n">
+        <v>1.1555</v>
+      </c>
+      <c r="F37" s="51" t="n">
+        <v>0.86542622</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
         </is>
@@ -12057,12 +12320,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BANCO BILBAO VIZCAYA ARGENTARIA, S.A.</t>
+          <t>BBVACNC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>BBVA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -12070,7 +12333,11 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Contract rental invoices</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -12951,7 +13218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13076,22 +13343,22 @@
     <row r="9" ht="12" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1272</v>
+        <v>12636</v>
       </c>
     </row>
     <row r="10" ht="12" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -13100,13 +13367,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1596</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -13115,13 +13382,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1938</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13130,13 +13397,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1617</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13145,13 +13412,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1629</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13160,43 +13427,43 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1767</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>471</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>744</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -13205,13 +13472,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>741</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -13220,13 +13487,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>567</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13235,22 +13502,67 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>471</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="21" ht="12" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>202606</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C22" t="n">
         <v>543</v>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -13459,10 +13771,10 @@
         <v>20</v>
       </c>
       <c r="J4" s="54" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K4" s="54" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" s="54" t="n">
         <v>0</v>
@@ -13477,7 +13789,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="54" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="Q4" s="54" t="n"/>
     </row>
@@ -13508,10 +13820,10 @@
         <v>15</v>
       </c>
       <c r="J5" s="55" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" s="55" t="n">
         <v>0</v>
@@ -13526,7 +13838,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="55" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="Q5" s="55" t="n"/>
     </row>
@@ -13560,7 +13872,7 @@
         <v>14</v>
       </c>
       <c r="K6" s="57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L6" s="57" t="n">
         <v>0</v>
@@ -13575,7 +13887,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="57" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="Q6" s="57" t="n"/>
     </row>
@@ -13607,7 +13919,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -13622,7 +13934,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
@@ -13653,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -13668,7 +13980,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -13699,7 +14011,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -13714,7 +14026,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="12" customHeight="1">
@@ -13745,7 +14057,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -13760,7 +14072,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1">
@@ -13791,7 +14103,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -13806,7 +14118,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1">
@@ -13837,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -13852,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1">
@@ -13883,7 +14195,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -13898,7 +14210,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1">
@@ -13929,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -13944,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1">
@@ -13975,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -13990,7 +14302,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
@@ -14021,7 +14333,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -14036,7 +14348,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
@@ -14066,7 +14378,7 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
@@ -14112,7 +14424,7 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
@@ -14159,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -14174,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1">
@@ -14205,7 +14517,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -14220,7 +14532,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1">
@@ -14250,7 +14562,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="57" t="n">
         <v>0</v>
@@ -14268,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q21" s="57" t="n"/>
     </row>
@@ -14296,10 +14608,10 @@
       <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
@@ -14315,7 +14627,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1">
@@ -14342,7 +14654,7 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="59" t="n">
+      <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
@@ -14388,7 +14700,7 @@
       <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="59" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
@@ -14624,7 +14936,7 @@
       <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="59" t="n">
+      <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
@@ -14674,7 +14986,7 @@
         <v>4</v>
       </c>
       <c r="J31" s="55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K31" s="55" t="n">
         <v>0</v>
@@ -14692,7 +15004,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q31" s="55" t="n"/>
     </row>
@@ -14720,10 +15032,10 @@
       <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
@@ -14739,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1">
@@ -14766,10 +15078,10 @@
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
@@ -14785,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1">
@@ -14812,10 +15124,10 @@
       <c r="I34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
@@ -14831,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1">
@@ -14858,10 +15170,10 @@
       <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
@@ -14877,7 +15189,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1">
@@ -14906,7 +15218,7 @@
       <c r="I36" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="59" t="n">
+      <c r="J36" s="57" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="57" t="n">
@@ -14957,10 +15269,10 @@
         <v>56</v>
       </c>
       <c r="J38" s="54" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K38" s="54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L38" s="54" t="n">
         <v>0</v>
@@ -14975,7 +15287,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="54" t="n">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="Q38" s="54" t="n"/>
     </row>
@@ -15006,10 +15318,10 @@
         <v>25</v>
       </c>
       <c r="J39" s="55" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="K39" s="55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L39" s="55" t="n">
         <v>0</v>
@@ -15024,7 +15336,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="55" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="Q39" s="55" t="n"/>
     </row>
@@ -15055,10 +15367,10 @@
         <v>10</v>
       </c>
       <c r="J40" s="57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K40" s="57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="57" t="n">
         <v>0</v>
@@ -15073,7 +15385,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="57" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Q40" s="57" t="n"/>
     </row>
@@ -15104,7 +15416,7 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
@@ -15148,10 +15460,10 @@
         <v>4</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -15166,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" ht="12" customHeight="1">
@@ -15193,7 +15505,7 @@
       <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="59" t="n">
+      <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
@@ -15239,10 +15551,10 @@
       <c r="I44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="59" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="n">
+      <c r="J44" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
@@ -15258,7 +15570,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" ht="12" customHeight="1">
@@ -15286,9 +15598,9 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
@@ -15304,7 +15616,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" ht="12" customHeight="1">
@@ -15334,7 +15646,7 @@
         <v>11</v>
       </c>
       <c r="J46" s="57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K46" s="57" t="n">
         <v>0</v>
@@ -15352,7 +15664,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="57" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q46" s="57" t="n"/>
     </row>
@@ -15380,10 +15692,10 @@
       <c r="I47" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
@@ -15399,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" ht="12" customHeight="1">
@@ -15426,10 +15738,10 @@
       <c r="I48" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
@@ -15445,7 +15757,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" ht="12" customHeight="1">
@@ -15472,10 +15784,10 @@
       <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
@@ -15491,7 +15803,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" ht="12" customHeight="1">
@@ -15567,7 +15879,7 @@
       <c r="J51" t="n">
         <v>7</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
@@ -15613,7 +15925,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" s="57" t="n">
         <v>0</v>
@@ -15631,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q52" s="57" t="n"/>
     </row>
@@ -15659,10 +15971,10 @@
       <c r="I53" t="n">
         <v>1</v>
       </c>
-      <c r="J53" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
@@ -15678,7 +15990,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" ht="12" customHeight="1">
@@ -15705,10 +16017,10 @@
       <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
@@ -15724,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" ht="12" customHeight="1">
@@ -15751,10 +16063,10 @@
       <c r="I55" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
@@ -15770,7 +16082,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" ht="12" customHeight="1">
@@ -15797,10 +16109,10 @@
       <c r="I56" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
@@ -15816,7 +16128,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" ht="12" customHeight="1">
@@ -15849,7 +16161,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="57" t="n">
         <v>0</v>
@@ -15864,7 +16176,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="57" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q57" s="57" t="n"/>
     </row>
@@ -15896,7 +16208,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -15911,7 +16223,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1">
@@ -15942,7 +16254,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -15957,7 +16269,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1"/>
@@ -15989,10 +16301,10 @@
         <v>31</v>
       </c>
       <c r="J62" s="55" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K62" s="55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="55" t="n">
         <v>0</v>
@@ -16007,7 +16319,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="55" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="Q62" s="55" t="n"/>
     </row>
@@ -16510,7 +16822,7 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
@@ -16694,11 +17006,11 @@
       <c r="I77" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="59" t="n">
+      <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -16713,7 +17025,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" ht="12" customHeight="1">
@@ -16744,7 +17056,7 @@
         <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -16759,7 +17071,7 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" ht="12" customHeight="1">
@@ -16881,7 +17193,7 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
@@ -16927,7 +17239,7 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
@@ -17111,7 +17423,7 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
@@ -17154,7 +17466,7 @@
       <c r="I87" t="n">
         <v>3</v>
       </c>
-      <c r="J87" s="59" t="n">
+      <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
@@ -17250,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17265,7 +17577,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" ht="12" customHeight="1">
@@ -17341,10 +17653,10 @@
         <v>28</v>
       </c>
       <c r="J91" s="57" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K91" s="57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="57" t="n">
         <v>0</v>
@@ -17359,7 +17671,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="57" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Q91" s="57" t="n"/>
     </row>
@@ -17387,7 +17699,7 @@
       <c r="I92" t="n">
         <v>1</v>
       </c>
-      <c r="J92" s="59" t="n">
+      <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
@@ -17436,7 +17748,7 @@
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
@@ -17479,7 +17791,7 @@
       <c r="I94" t="n">
         <v>6</v>
       </c>
-      <c r="J94" s="59" t="n">
+      <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
@@ -17525,10 +17837,10 @@
       <c r="I95" t="n">
         <v>1</v>
       </c>
-      <c r="J95" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
@@ -17544,7 +17856,7 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" ht="12" customHeight="1">
@@ -17574,7 +17886,7 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
@@ -17620,7 +17932,7 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="n">
@@ -17663,10 +17975,10 @@
       <c r="I98" t="n">
         <v>2</v>
       </c>
-      <c r="J98" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
+      <c r="J98" t="n">
+        <v>2</v>
+      </c>
+      <c r="K98" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
@@ -17682,7 +17994,7 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" ht="12" customHeight="1">
@@ -17712,7 +18024,7 @@
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
@@ -17756,9 +18068,9 @@
         <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" t="n">
+        <v>2</v>
+      </c>
+      <c r="K100" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L100" t="n">
@@ -17774,7 +18086,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" ht="12" customHeight="1">
@@ -17801,10 +18113,10 @@
       <c r="I101" t="n">
         <v>5</v>
       </c>
-      <c r="J101" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="K101" t="n">
+      <c r="J101" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="n">
@@ -17820,7 +18132,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" ht="12" customHeight="1">
@@ -17850,7 +18162,7 @@
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L102" t="n">
@@ -17897,7 +18209,7 @@
         <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -17912,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1">
@@ -17942,8 +18254,8 @@
       <c r="J104" t="n">
         <v>3</v>
       </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="K104" s="59" t="n">
+        <v>1</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -17958,7 +18270,7 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1">
@@ -17988,7 +18300,7 @@
       <c r="J105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
@@ -18034,7 +18346,7 @@
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L106" t="n">
@@ -18077,10 +18389,10 @@
       <c r="I107" t="n">
         <v>1</v>
       </c>
-      <c r="J107" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="n">
@@ -18096,7 +18408,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1">
@@ -18126,7 +18438,7 @@
       <c r="J108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K108" s="59" t="n">
         <v>0</v>
       </c>
       <c r="L108" t="n">
@@ -18171,7 +18483,7 @@
       <c r="I109" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="J109" s="59" t="n">
+      <c r="J109" s="57" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="57" t="n">
@@ -18220,7 +18532,7 @@
       <c r="I110" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="J110" s="59" t="n">
+      <c r="J110" s="57" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="57" t="n">
@@ -18475,9 +18787,8 @@
       <c r="I5" s="50" t="n">
         <v>7194.7</v>
       </c>
-      <c r="J5" s="50">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$2,'g-expenses-sl'!$D:$D,"marketing",'g-expenses-sl'!$F:$F,"uk")</f>
-        <v/>
+      <c r="J5" s="50" t="n">
+        <v>7543.77</v>
       </c>
       <c r="K5" s="50">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$2,'g-expenses-sl'!$D:$D,"marketing",'g-expenses-sl'!$F:$F,"uk")</f>
@@ -18529,9 +18840,8 @@
       <c r="I6" s="50" t="n">
         <v>1767</v>
       </c>
-      <c r="J6" s="50">
-        <f>SUMIFS('i-royalties-scope-sl'!$C:$C,'i-royalties-scope-sl'!$A:$A,J$2,'i-royalties-scope-sl'!$B:$B,"uk")</f>
-        <v/>
+      <c r="J6" s="50" t="n">
+        <v>1692</v>
       </c>
       <c r="K6" s="50">
         <f>SUMIFS('i-royalties-scope-sl'!$C:$C,'i-royalties-scope-sl'!$A:$A,K$2,'i-royalties-scope-sl'!$B:$B,"uk")</f>
@@ -18583,9 +18893,8 @@
       <c r="I7" s="50" t="n">
         <v>2313.27</v>
       </c>
-      <c r="J7" s="50">
-        <f>'P&amp;G-SL'!J95*VLOOKUP("pct_staff_uk",params!$A:$B,2,0)</f>
-        <v/>
+      <c r="J7" s="50" t="n">
+        <v>2327.27</v>
       </c>
       <c r="K7" s="50">
         <f>'P&amp;G-SL'!K95*VLOOKUP("pct_staff_uk",params!$A:$B,2,0)</f>
@@ -18637,9 +18946,8 @@
       <c r="I8" s="50" t="n">
         <v>1245.35</v>
       </c>
-      <c r="J8" s="50">
-        <f>('P&amp;G-SL'!J98+'P&amp;G-SL'!J114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
-        <v/>
+      <c r="J8" s="50" t="n">
+        <v>1160.58</v>
       </c>
       <c r="K8" s="50">
         <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
@@ -18858,9 +19166,8 @@
       <c r="I13" s="50" t="n">
         <v>1960.9</v>
       </c>
-      <c r="J13" s="50">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$2,'g-expenses-sl'!$D:$D,"marketing",'g-expenses-sl'!$F:$F,"us")</f>
-        <v/>
+      <c r="J13" s="50" t="n">
+        <v>2731.39</v>
       </c>
       <c r="K13" s="50">
         <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$2,'g-expenses-sl'!$D:$D,"marketing",'g-expenses-sl'!$F:$F,"us")</f>
@@ -18912,9 +19219,8 @@
       <c r="I14" s="50" t="n">
         <v>543</v>
       </c>
-      <c r="J14" s="50">
-        <f>SUMIFS('i-royalties-scope-sl'!$C:$C,'i-royalties-scope-sl'!$A:$A,J$2,'i-royalties-scope-sl'!$B:$B,"us")</f>
-        <v/>
+      <c r="J14" s="50" t="n">
+        <v>498</v>
       </c>
       <c r="K14" s="50">
         <f>SUMIFS('i-royalties-scope-sl'!$C:$C,'i-royalties-scope-sl'!$A:$A,K$2,'i-royalties-scope-sl'!$B:$B,"us")</f>
@@ -18966,9 +19272,8 @@
       <c r="I15" s="50" t="n">
         <v>1542.18</v>
       </c>
-      <c r="J15" s="50">
-        <f>'P&amp;G-SL'!J95*VLOOKUP("pct_staff_us",params!$A:$B,2,0)</f>
-        <v/>
+      <c r="J15" s="50" t="n">
+        <v>1551.51</v>
       </c>
       <c r="K15" s="50">
         <f>'P&amp;G-SL'!K95*VLOOKUP("pct_staff_us",params!$A:$B,2,0)</f>
@@ -19020,9 +19325,8 @@
       <c r="I16" s="50" t="n">
         <v>830.23</v>
       </c>
-      <c r="J16" s="50">
-        <f>('P&amp;G-SL'!J98+'P&amp;G-SL'!J114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
-        <v/>
+      <c r="J16" s="50" t="n">
+        <v>773.72</v>
       </c>
       <c r="K16" s="50">
         <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
@@ -19312,7 +19616,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31T10:25:14Z</t>
+          <t>2026-08-10T21:59:52Z</t>
         </is>
       </c>
     </row>
@@ -19370,7 +19674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19478,7 +19782,7 @@
         </is>
       </c>
       <c r="E3" s="50" t="n">
-        <v>5472.24</v>
+        <v>5482.24</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -19494,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="I3" s="50" t="n">
-        <v>5472.24</v>
+        <v>5482.24</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -19622,7 +19926,7 @@
         </is>
       </c>
       <c r="E6" s="50" t="n">
-        <v>20230.26</v>
+        <v>20271.04</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -19638,7 +19942,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="50" t="n">
-        <v>20230.26</v>
+        <v>20271.04</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -19670,7 +19974,7 @@
         </is>
       </c>
       <c r="E7" s="50" t="n">
-        <v>61194.44</v>
+        <v>61194.43</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -19686,7 +19990,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="50" t="n">
-        <v>61194.44</v>
+        <v>61194.43</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -19718,7 +20022,7 @@
         </is>
       </c>
       <c r="E8" s="50" t="n">
-        <v>25562.13</v>
+        <v>25590.34</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -19734,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="50" t="n">
-        <v>25562.13</v>
+        <v>25590.34</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -19766,7 +20070,7 @@
         </is>
       </c>
       <c r="E9" s="50" t="n">
-        <v>18488.36</v>
+        <v>18538.59</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -19782,7 +20086,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="50" t="n">
-        <v>18488.36</v>
+        <v>18538.59</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -20006,7 +20310,7 @@
         </is>
       </c>
       <c r="E14" s="50" t="n">
-        <v>6064.69</v>
+        <v>6077.94</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -20022,7 +20326,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="50" t="n">
-        <v>6064.69</v>
+        <v>6077.94</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -20102,7 +20406,7 @@
         </is>
       </c>
       <c r="E16" s="50" t="n">
-        <v>19166.62</v>
+        <v>19196.42</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -20118,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="50" t="n">
-        <v>19166.62</v>
+        <v>19196.42</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -20198,7 +20502,7 @@
         </is>
       </c>
       <c r="E18" s="50" t="n">
-        <v>73214.46000000001</v>
+        <v>73214.47</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -20214,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="50" t="n">
-        <v>73214.46000000001</v>
+        <v>73214.47</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -20246,7 +20550,7 @@
         </is>
       </c>
       <c r="E19" s="50" t="n">
-        <v>27467.98</v>
+        <v>27502.63</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -20262,7 +20566,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="50" t="n">
-        <v>27467.98</v>
+        <v>27502.63</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -20342,7 +20646,7 @@
         </is>
       </c>
       <c r="E21" s="50" t="n">
-        <v>20013.28</v>
+        <v>20044.86</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -20358,7 +20662,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="50" t="n">
-        <v>20013.28</v>
+        <v>20044.86</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -20534,7 +20838,7 @@
         </is>
       </c>
       <c r="E25" s="50" t="n">
-        <v>5410.61</v>
+        <v>5428.11</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -20550,7 +20854,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="50" t="n">
-        <v>5410.61</v>
+        <v>5428.11</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -20630,7 +20934,7 @@
         </is>
       </c>
       <c r="E27" s="50" t="n">
-        <v>24820.62</v>
+        <v>24871.75</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -20646,7 +20950,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="50" t="n">
-        <v>24820.62</v>
+        <v>24871.75</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -20678,7 +20982,7 @@
         </is>
       </c>
       <c r="E28" s="50" t="n">
-        <v>70845.75</v>
+        <v>70845.74000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -20694,7 +20998,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="50" t="n">
-        <v>70845.75</v>
+        <v>70845.74000000001</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -20726,7 +21030,7 @@
         </is>
       </c>
       <c r="E29" s="50" t="n">
-        <v>31210.51</v>
+        <v>31270.44</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -20742,7 +21046,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="50" t="n">
-        <v>31210.51</v>
+        <v>31270.44</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -20822,7 +21126,7 @@
         </is>
       </c>
       <c r="E31" s="50" t="n">
-        <v>20244.06</v>
+        <v>20258.56</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -20838,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="50" t="n">
-        <v>20244.06</v>
+        <v>20258.56</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -20966,7 +21270,7 @@
         </is>
       </c>
       <c r="E34" s="50" t="n">
-        <v>4085.09</v>
+        <v>4107.27</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -20982,7 +21286,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="50" t="n">
-        <v>4085.09</v>
+        <v>4107.27</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -21014,7 +21318,7 @@
         </is>
       </c>
       <c r="E35" s="50" t="n">
-        <v>151.72</v>
+        <v>159.19</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -21030,7 +21334,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="50" t="n">
-        <v>151.72</v>
+        <v>159.19</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -21062,7 +21366,7 @@
         </is>
       </c>
       <c r="E36" s="50" t="n">
-        <v>19303.41</v>
+        <v>19358.29</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -21078,7 +21382,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="50" t="n">
-        <v>19303.41</v>
+        <v>19358.29</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -21206,7 +21510,7 @@
         </is>
       </c>
       <c r="E39" s="50" t="n">
-        <v>27169.89</v>
+        <v>27181.78</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -21222,7 +21526,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="50" t="n">
-        <v>27169.89</v>
+        <v>27181.78</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -21302,7 +21606,7 @@
         </is>
       </c>
       <c r="E41" s="50" t="n">
-        <v>18345.04</v>
+        <v>18468.95</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -21318,7 +21622,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="50" t="n">
-        <v>18345.04</v>
+        <v>18468.95</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -21446,7 +21750,7 @@
         </is>
       </c>
       <c r="E44" s="50" t="n">
-        <v>5461.52</v>
+        <v>5463.67</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -21462,7 +21766,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="50" t="n">
-        <v>5461.52</v>
+        <v>5463.67</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -21542,7 +21846,7 @@
         </is>
       </c>
       <c r="E46" s="50" t="n">
-        <v>16757.78</v>
+        <v>16788.44</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -21558,7 +21862,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="50" t="n">
-        <v>16757.78</v>
+        <v>16788.44</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -21638,7 +21942,7 @@
         </is>
       </c>
       <c r="E48" s="50" t="n">
-        <v>71605.44</v>
+        <v>71605.42999999999</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -21654,7 +21958,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="50" t="n">
-        <v>71605.44</v>
+        <v>71605.42999999999</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -21686,7 +21990,7 @@
         </is>
       </c>
       <c r="E49" s="50" t="n">
-        <v>26658.58</v>
+        <v>26689.09</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -21702,7 +22006,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="50" t="n">
-        <v>26658.58</v>
+        <v>26689.09</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -21782,7 +22086,7 @@
         </is>
       </c>
       <c r="E51" s="50" t="n">
-        <v>17195.67</v>
+        <v>17210.15</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -21798,7 +22102,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="50" t="n">
-        <v>17195.67</v>
+        <v>17210.15</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -22502,7 +22806,7 @@
         </is>
       </c>
       <c r="E66" s="50" t="n">
-        <v>4831.74</v>
+        <v>4858.31</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -22518,7 +22822,7 @@
         <v>1</v>
       </c>
       <c r="I66" s="50" t="n">
-        <v>4831.74</v>
+        <v>4858.31</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -22550,7 +22854,7 @@
         </is>
       </c>
       <c r="E67" s="50" t="n">
-        <v>4128.32</v>
+        <v>4442.82</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -22566,7 +22870,7 @@
         <v>1</v>
       </c>
       <c r="I67" s="50" t="n">
-        <v>4128.32</v>
+        <v>4442.82</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -22646,7 +22950,7 @@
         </is>
       </c>
       <c r="E69" s="50" t="n">
-        <v>17211.56</v>
+        <v>17581.98</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -22662,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="I69" s="50" t="n">
-        <v>17211.56</v>
+        <v>17581.98</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -22694,7 +22998,7 @@
         </is>
       </c>
       <c r="E70" s="50" t="n">
-        <v>1650.84</v>
+        <v>1697.61</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -22710,7 +23014,7 @@
         <v>1</v>
       </c>
       <c r="I70" s="50" t="n">
-        <v>1650.84</v>
+        <v>1697.61</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -22742,7 +23046,7 @@
         </is>
       </c>
       <c r="E71" s="50" t="n">
-        <v>64027.01</v>
+        <v>75419.2</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -22758,7 +23062,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="50" t="n">
-        <v>64027.01</v>
+        <v>75419.2</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -22790,7 +23094,7 @@
         </is>
       </c>
       <c r="E72" s="50" t="n">
-        <v>29481.73</v>
+        <v>30091.81</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -22806,7 +23110,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="50" t="n">
-        <v>29481.73</v>
+        <v>30091.81</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -22886,7 +23190,7 @@
         </is>
       </c>
       <c r="E74" s="50" t="n">
-        <v>16704.91</v>
+        <v>17113.21</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -22902,7 +23206,7 @@
         <v>1</v>
       </c>
       <c r="I74" s="50" t="n">
-        <v>16704.91</v>
+        <v>17113.21</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -22982,7 +23286,7 @@
         </is>
       </c>
       <c r="E76" s="50" t="n">
-        <v>2989.75</v>
+        <v>3070.58</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -22998,7 +23302,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="50" t="n">
-        <v>2989.75</v>
+        <v>3070.58</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -23030,7 +23334,7 @@
         </is>
       </c>
       <c r="E77" s="50" t="n">
-        <v>4806.7</v>
+        <v>4336.431788617886</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -23046,7 +23350,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="50" t="n">
-        <v>4806.7</v>
+        <v>4336.43</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -23078,7 +23382,7 @@
         </is>
       </c>
       <c r="E78" s="50" t="n">
-        <v>2889.06</v>
+        <v>3046.3</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -23094,7 +23398,7 @@
         <v>1</v>
       </c>
       <c r="I78" s="50" t="n">
-        <v>2889.06</v>
+        <v>3046.3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -23151,6 +23455,582 @@
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+    </row>
+    <row r="80" ht="12" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="E80" s="50" t="n">
+        <v>2062.17</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H80" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="50" t="n">
+        <v>2062.17</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81" ht="12" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E81" s="50" t="n">
+        <v>2039.02</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H81" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="50" t="n">
+        <v>2039.02</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82" ht="12" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E82" s="50" t="n">
+        <v>19210.62</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H82" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="50" t="n">
+        <v>19210.62</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83" ht="12" customHeight="1">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E83" s="50" t="n">
+        <v>7854.36</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H83" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="50" t="n">
+        <v>7854.36</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84" ht="12" customHeight="1">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E84" s="50" t="n">
+        <v>13571.05</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H84" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="50" t="n">
+        <v>13571.05</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85" ht="12" customHeight="1">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E85" s="50" t="n">
+        <v>19060.68</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H85" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="50" t="n">
+        <v>19060.68</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86" ht="12" customHeight="1">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E86" s="50" t="n">
+        <v>10662.8</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H86" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="50" t="n">
+        <v>10662.8</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87" ht="12" customHeight="1">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E87" s="50" t="n">
+        <v>7020.86</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H87" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="50" t="n">
+        <v>7020.86</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88" ht="12" customHeight="1">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E88" s="50" t="n">
+        <v>1938.9</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H88" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="50" t="n">
+        <v>1938.9</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89" ht="12" customHeight="1">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E89" s="50" t="n">
+        <v>11435.23</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H89" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="50" t="n">
+        <v>11435.23</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90" ht="12" customHeight="1">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E90" s="50" t="n">
+        <v>1338</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H90" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="50" t="n">
+        <v>1338</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91" ht="12" customHeight="1">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E91" s="50" t="n">
+        <v>17609.98</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H91" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="50" t="n">
+        <v>17609.98</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23166,7 +24046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23868,6 +24748,62 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="12" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="E14" s="50" t="n">
+        <v>1314.69</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H14" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="50" t="n">
+        <v>1314.69</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>2026-0038</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Zof1st-SRtECrpmnABzJMDM_JirZWIZv/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'P&amp;G-SL'!A1" display="&lt;- Volver a P&amp;G-SL"/>
@@ -23882,6 +24818,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24492,7 +25429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25807,6 +26744,230 @@
       <c r="L24" t="inlineStr">
         <is>
           <t>https://drive.google.com/file/d/1GTB7C_m8wqI5ZcLtddZ9CbMD79Quoac-/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>renting_coche</t>
+        </is>
+      </c>
+      <c r="E25" s="50" t="n">
+        <v>451.25</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H25" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="50" t="n">
+        <v>451.25</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K25" s="52" t="inlineStr">
+        <is>
+          <t>2026-0037</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jiSSrgB2YZB08Mp8ipw1vCzQzSqCxQ0M/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Inc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E26" s="50" t="n">
+        <v>5554.62</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H26" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="50" t="n">
+        <v>5554.62</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K26" s="52" t="inlineStr">
+        <is>
+          <t>2026-0034</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jMiEonYuJ1w4GrQplnTJlicvIVyJGOJ9/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="12" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ltd</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E27" s="50" t="n">
+        <v>12723.62</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H27" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="50" t="n">
+        <v>12723.62</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K27" s="52" t="inlineStr">
+        <is>
+          <t>2026-0035</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1p5kDIwFbkE7uMI4VEuHP3X2RbTa9kt-R/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>QHANDS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>renting_cnc</t>
+        </is>
+      </c>
+      <c r="E28" s="50" t="n">
+        <v>2089.49</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H28" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="50" t="n">
+        <v>2089.49</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="K28" s="52" t="inlineStr">
+        <is>
+          <t>2026-0036</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1ZAvhx25JZaBE6LpWsSvd6L9ezDZBSrPK/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -25835,6 +26996,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25846,7 +27011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -26604,6 +27769,118 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="12" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Inc</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E15" s="50" t="n">
+        <v>5554.62</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H15" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="50" t="n">
+        <v>5554.62</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K15" s="52" t="inlineStr">
+        <is>
+          <t>2026-0034</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jMiEonYuJ1w4GrQplnTJlicvIVyJGOJ9/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="12" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ltd</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>shared_services</t>
+        </is>
+      </c>
+      <c r="E16" s="50" t="n">
+        <v>12723.62</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H16" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="50" t="n">
+        <v>12723.62</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>documents:shared_services</t>
+        </is>
+      </c>
+      <c r="K16" s="52" t="inlineStr">
+        <is>
+          <t>2026-0035</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1p5kDIwFbkE7uMI4VEuHP3X2RbTa9kt-R/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" location="'P&amp;G-SL'!A1" display="&lt;- Volver a P&amp;G-SL"/>
@@ -26619,6 +27896,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26630,7 +27909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N391"/>
+  <dimension ref="A1:N420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -47137,10 +48416,10 @@
         </is>
       </c>
       <c r="J327" s="51" t="n">
-        <v>0.87138376</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="K327" s="50" t="n">
-        <v>97.41</v>
+        <v>97.34</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -48349,22 +49628,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>APPHOTOES</t>
         </is>
       </c>
       <c r="F347" t="inlineStr"/>
       <c r="G347" s="50" t="n">
-        <v>9.91</v>
+        <v>3145.08</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
@@ -48380,7 +49659,7 @@
         <v>1</v>
       </c>
       <c r="K347" s="50" t="n">
-        <v>9.91</v>
+        <v>3145.08</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -48389,12 +49668,12 @@
       </c>
       <c r="M347" s="52" t="inlineStr">
         <is>
-          <t>04946-17326623</t>
+          <t>1-9619</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/15GVedhY_Gl0PpYtjqFX3NWCQlKZKQ8cn/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1KmNLzVWPLJO5hNqy-pXe-5dZqwbMhvJ5/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48416,17 +49695,17 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>CLARIS</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="F348" t="inlineStr"/>
       <c r="G348" s="50" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -48442,7 +49721,7 @@
         <v>1</v>
       </c>
       <c r="K348" s="50" t="n">
-        <v>808.08</v>
+        <v>9.91</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -48451,12 +49730,12 @@
       </c>
       <c r="M348" s="52" t="inlineStr">
         <is>
-          <t>F02310/26</t>
+          <t>04946-17326623</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gGxwu4sgSQALHI5GuZLsNjcbCAVNHe2R/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/15GVedhY_Gl0PpYtjqFX3NWCQlKZKQ8cn/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48473,22 +49752,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>DCT</t>
+          <t>CLARIS</t>
         </is>
       </c>
       <c r="F349" t="inlineStr"/>
       <c r="G349" s="50" t="n">
-        <v>3140.56</v>
+        <v>808.08</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -48504,7 +49783,7 @@
         <v>1</v>
       </c>
       <c r="K349" s="50" t="n">
-        <v>3140.56</v>
+        <v>808.08</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -48513,12 +49792,12 @@
       </c>
       <c r="M349" s="52" t="inlineStr">
         <is>
-          <t>26-1294</t>
+          <t>F02310/26</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tff0GJT8Ypaz3kXZw2X6rnZkrJvcGYKR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1gGxwu4sgSQALHI5GuZLsNjcbCAVNHe2R/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48535,26 +49814,26 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>CORREOS</t>
         </is>
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" s="50" t="n">
-        <v>120</v>
+        <v>147.34</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48563,10 +49842,10 @@
         </is>
       </c>
       <c r="J350" s="51" t="n">
-        <v>0.87138376</v>
+        <v>1</v>
       </c>
       <c r="K350" s="50" t="n">
-        <v>104.57</v>
+        <v>147.34</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -48575,12 +49854,12 @@
       </c>
       <c r="M350" s="52" t="inlineStr">
         <is>
-          <t>INC-07-2026-129902</t>
+          <t>4004748097</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12aAWFEEdzb5j2tV4l0A0oQ8GR9NHRtgI/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/105yum9abnuLjnGrZ0fk1aTcY8rWXZC1H/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48597,26 +49876,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>HANNUN</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>administration</t>
-        </is>
-      </c>
+          <t>CORREOSCAN</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
       <c r="G351" s="50" t="n">
-        <v>1555.85</v>
+        <v>24.96</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -48632,7 +49907,7 @@
         <v>1</v>
       </c>
       <c r="K351" s="50" t="n">
-        <v>1555.85</v>
+        <v>24.96</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -48641,12 +49916,12 @@
       </c>
       <c r="M351" s="52" t="inlineStr">
         <is>
-          <t>VTA/26-026373</t>
+          <t>4004748099</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1B3io5YGmR3RT24Qbh5AQXrPR9ViffHIS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-cC_35Uai3G4eBk53chzRtZ9meVc3njq/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48663,26 +49938,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>HANNUN</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>office</t>
-        </is>
-      </c>
+          <t>DCT</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
       <c r="G352" s="50" t="n">
-        <v>175</v>
+        <v>3140.56</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
@@ -48698,7 +49969,7 @@
         <v>1</v>
       </c>
       <c r="K352" s="50" t="n">
-        <v>175</v>
+        <v>3140.56</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -48707,12 +49978,12 @@
       </c>
       <c r="M352" s="52" t="inlineStr">
         <is>
-          <t>VTA/26-026372</t>
+          <t>26-1294</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CrwqKvYiDQBox1HOG9l8DscgX3UBvWbS/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1tff0GJT8Ypaz3kXZw2X6rnZkrJvcGYKR/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48729,22 +50000,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" s="50" t="n">
-        <v>10.9</v>
+        <v>4200.93</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
@@ -48760,7 +50031,7 @@
         <v>1</v>
       </c>
       <c r="K353" s="50" t="n">
-        <v>10.9</v>
+        <v>4200.93</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -48769,12 +50040,12 @@
       </c>
       <c r="M353" s="52" t="inlineStr">
         <is>
-          <t>087001068400</t>
+          <t>26-1415</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1R23fupAyC7WD-BZwliBegEBTxNl2N03B/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10PCzf6eS9w8yDlLU8jmGdLDQmLHv9Vvx/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48791,22 +50062,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" s="50" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
@@ -48822,7 +50093,7 @@
         <v>1</v>
       </c>
       <c r="K354" s="50" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -48831,12 +50102,12 @@
       </c>
       <c r="M354" s="52" t="inlineStr">
         <is>
-          <t>MC260008794424</t>
+          <t>26-1416</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hoWg6TfcG-NPv7hMfITu-oKnH2oVr_eX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1on2ohuuHhS2a_OpB3rPmCg9Lmfglx3bp/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48853,22 +50124,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>GLS</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" s="50" t="n">
-        <v>30.87</v>
+        <v>14994.95</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
@@ -48884,7 +50155,7 @@
         <v>1</v>
       </c>
       <c r="K355" s="50" t="n">
-        <v>30.87</v>
+        <v>14994.95</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -48893,12 +50164,12 @@
       </c>
       <c r="M355" s="52" t="inlineStr">
         <is>
-          <t>G171225587</t>
+          <t>20260409</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hPMWmwoSk_E-NyCq2uC5-Bms9wRJESlM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1-CmJS7W5hLkYXodnYqYAWH-nCeyfb_sB/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48920,17 +50191,21 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>NODA</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
       <c r="G356" s="50" t="n">
-        <v>180</v>
+        <v>26754.75</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -48946,7 +50221,7 @@
         <v>1</v>
       </c>
       <c r="K356" s="50" t="n">
-        <v>180</v>
+        <v>26754.75</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -48955,12 +50230,12 @@
       </c>
       <c r="M356" s="52" t="inlineStr">
         <is>
-          <t>160/26</t>
+          <t>5649593148</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1MjbvGYnouuMkppyPq0weIAEzTe4k5xge/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZEjPdXs0QGQcMNILEN1qxcxJpfd6nGir/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -48982,21 +50257,21 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>chatgpt_plus</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G357" s="50" t="n">
-        <v>85.12</v>
+        <v>4688.42</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
@@ -49012,7 +50287,7 @@
         <v>1</v>
       </c>
       <c r="K357" s="50" t="n">
-        <v>85.12</v>
+        <v>4688.42</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -49021,12 +50296,12 @@
       </c>
       <c r="M357" s="52" t="inlineStr">
         <is>
-          <t>7BSDV5AM-0004</t>
+          <t>5649593148</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1zz5LASlTYsQglYZHAdlobUGBURvgCxBV/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1viohE5lUvD6jia3JMaY-JhxcvpW4oBjj/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49048,21 +50323,21 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>chatgpt_plus</t>
+          <t>us</t>
         </is>
       </c>
       <c r="G358" s="50" t="n">
-        <v>19.01</v>
+        <v>1765.24</v>
       </c>
       <c r="H358" t="inlineStr">
         <is>
@@ -49078,7 +50353,7 @@
         <v>1</v>
       </c>
       <c r="K358" s="50" t="n">
-        <v>19.01</v>
+        <v>1765.24</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -49087,12 +50362,12 @@
       </c>
       <c r="M358" s="52" t="inlineStr">
         <is>
-          <t>HPTYPXYP-0001</t>
+          <t>5649593148</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1XiV0belx8HMpXLhBrEEw7NdwOr6W6EpP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1ZEjPdXs0QGQcMNILEN1qxcxJpfd6nGir/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49109,26 +50384,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>manufacturing</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>PRESSING</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>manufacturing</t>
-        </is>
-      </c>
+          <t>GOOGLEWORKSPACE</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" s="50" t="n">
-        <v>350.41</v>
+        <v>210.6</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
@@ -49144,7 +50415,7 @@
         <v>1</v>
       </c>
       <c r="K359" s="50" t="n">
-        <v>350.41</v>
+        <v>210.6</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -49153,12 +50424,12 @@
       </c>
       <c r="M359" s="52" t="inlineStr">
         <is>
-          <t>R-2026-0001</t>
+          <t>5642106636</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1BgipjaNJok28U6NHH7hb1HzCn7H_8YYR/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1f2xATXwv_4IPI825PqzPtW6NVkkVHVv3/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49185,16 +50456,16 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" s="50" t="n">
-        <v>372.16</v>
+        <v>120</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49203,10 +50474,10 @@
         </is>
       </c>
       <c r="J360" s="51" t="n">
-        <v>1</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="K360" s="50" t="n">
-        <v>372.16</v>
+        <v>104.48</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -49215,12 +50486,12 @@
       </c>
       <c r="M360" s="52" t="inlineStr">
         <is>
-          <t>241860</t>
+          <t>INC-07-2026-129902</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1rfPfdJcTvizW0eXGbWDtwHLLG8g79BXM/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/12aAWFEEdzb5j2tV4l0A0oQ8GR9NHRtgI/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49242,17 +50513,21 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>REVER</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
       <c r="G361" s="50" t="n">
-        <v>256.5</v>
+        <v>1555.85</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
@@ -49268,7 +50543,7 @@
         <v>1</v>
       </c>
       <c r="K361" s="50" t="n">
-        <v>256.5</v>
+        <v>1555.85</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -49277,12 +50552,12 @@
       </c>
       <c r="M361" s="52" t="inlineStr">
         <is>
-          <t>RVR-21729</t>
+          <t>VTA/26-026373</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/17YPz8z7fRt7mMpHRe7X63aN95sJfrkid/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1B3io5YGmR3RT24Qbh5AQXrPR9ViffHIS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49304,17 +50579,21 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>REVER</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
       <c r="G362" s="50" t="n">
-        <v>256.5</v>
+        <v>175</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
@@ -49330,7 +50609,7 @@
         <v>1</v>
       </c>
       <c r="K362" s="50" t="n">
-        <v>256.5</v>
+        <v>175</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -49339,12 +50618,12 @@
       </c>
       <c r="M362" s="52" t="inlineStr">
         <is>
-          <t>RVR-21873</t>
+          <t>VTA/26-026372</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1tSGPsHHVzqmLGDRBLKLoeEggwrJqW_6L/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CrwqKvYiDQBox1HOG9l8DscgX3UBvWbS/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49371,12 +50650,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" s="50" t="n">
-        <v>79</v>
+        <v>10.9</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
@@ -49392,7 +50671,7 @@
         <v>1</v>
       </c>
       <c r="K363" s="50" t="n">
-        <v>79</v>
+        <v>10.9</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -49401,12 +50680,12 @@
       </c>
       <c r="M363" s="52" t="inlineStr">
         <is>
-          <t>RVR-22332</t>
+          <t>087001068400</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z4saK7F3rxKzXrumdfYopy3wLeFqH0Dt/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1R23fupAyC7WD-BZwliBegEBTxNl2N03B/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49433,16 +50712,16 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
       <c r="G364" s="50" t="n">
-        <v>3291.42</v>
+        <v>637.53</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -49451,10 +50730,10 @@
         </is>
       </c>
       <c r="J364" s="51" t="n">
-        <v>0.87138376</v>
+        <v>1</v>
       </c>
       <c r="K364" s="50" t="n">
-        <v>2868.09</v>
+        <v>637.53</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -49463,12 +50742,12 @@
       </c>
       <c r="M364" s="52" t="inlineStr">
         <is>
-          <t>563465757</t>
+          <t>B5F7DF3C-8814</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/12u1CWpL1978NM0H-5y0u3Q9eDkS_FVGw/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1xkDNQVgvDbKS0XPUvrqCWhD2yYlrK7bM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49495,12 +50774,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>SIMPLYCOM</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" s="50" t="n">
-        <v>0.54</v>
+        <v>180</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
@@ -49516,7 +50795,7 @@
         <v>1</v>
       </c>
       <c r="K365" s="50" t="n">
-        <v>0.54</v>
+        <v>180</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -49525,12 +50804,12 @@
       </c>
       <c r="M365" s="52" t="inlineStr">
         <is>
-          <t>4727397</t>
+          <t>B5F7DF3C-9009</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1vWhd7Pa5SP43onRKws4nymWiU7NozmOg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1TQOqESE58wutCec5u4A8s_v-UIhjpHv9/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49552,17 +50831,17 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="F366" t="inlineStr"/>
       <c r="G366" s="50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
@@ -49578,7 +50857,7 @@
         <v>1</v>
       </c>
       <c r="K366" s="50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -49587,12 +50866,12 @@
       </c>
       <c r="M366" s="52" t="inlineStr">
         <is>
-          <t>7/2781</t>
+          <t>MC260008794424</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1z8NVoi-_e47R6qkIxAaXaFscoze8wk2b/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hoWg6TfcG-NPv7hMfITu-oKnH2oVr_eX/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49609,22 +50888,26 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
       <c r="G367" s="50" t="n">
-        <v>-569.03</v>
+        <v>22797.4</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
@@ -49640,7 +50923,7 @@
         <v>1</v>
       </c>
       <c r="K367" s="50" t="n">
-        <v>-569.03</v>
+        <v>22797.4</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -49649,12 +50932,12 @@
       </c>
       <c r="M367" s="52" t="inlineStr">
         <is>
-          <t>2003660927</t>
+          <t>254615706</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/11-v2MJhXEqPk_yYCx2KlK8ou1Hj1nl96/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14d6G9EnHw4BjspnmKxC5OekHbUuFSj5t/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49671,22 +50954,26 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
       <c r="G368" s="50" t="n">
-        <v>509.48</v>
+        <v>2855.35</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
@@ -49702,7 +50989,7 @@
         <v>1</v>
       </c>
       <c r="K368" s="50" t="n">
-        <v>509.48</v>
+        <v>2855.35</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -49711,12 +50998,12 @@
       </c>
       <c r="M368" s="52" t="inlineStr">
         <is>
-          <t>327870911</t>
+          <t>254615706</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/16ubitUS_HwiWCAlQIEN9NuPpQ3Kiu4wg/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14d6G9EnHw4BjspnmKxC5OekHbUuFSj5t/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49733,22 +51020,26 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G369" s="50" t="n">
-        <v>853.66</v>
+        <v>966.15</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -49764,7 +51055,7 @@
         <v>1</v>
       </c>
       <c r="K369" s="50" t="n">
-        <v>853.66</v>
+        <v>966.15</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -49773,12 +51064,12 @@
       </c>
       <c r="M369" s="52" t="inlineStr">
         <is>
-          <t>327903065</t>
+          <t>254615706</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1hjw_XrPrz9bJ96OfjFlmMQIFAS8EGuwO/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/14d6G9EnHw4BjspnmKxC5OekHbUuFSj5t/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49795,22 +51086,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
       <c r="G370" s="50" t="n">
-        <v>1336.55</v>
+        <v>30.87</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
@@ -49826,7 +51117,7 @@
         <v>1</v>
       </c>
       <c r="K370" s="50" t="n">
-        <v>1336.55</v>
+        <v>30.87</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -49835,12 +51126,12 @@
       </c>
       <c r="M370" s="52" t="inlineStr">
         <is>
-          <t>327934792</t>
+          <t>G171225587</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1A2tjqFyfnDai7ZyuG3PAxaNkx_P1PrBZ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1hPMWmwoSk_E-NyCq2uC5-Bms9wRJESlM/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49857,22 +51148,22 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
       <c r="G371" s="50" t="n">
-        <v>5.23</v>
+        <v>45.7</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
@@ -49888,7 +51179,7 @@
         <v>1</v>
       </c>
       <c r="K371" s="50" t="n">
-        <v>5.23</v>
+        <v>45.7</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -49897,12 +51188,12 @@
       </c>
       <c r="M371" s="52" t="inlineStr">
         <is>
-          <t>838889502</t>
+          <t>G172096595</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/10MqUF30Ux7n5Fvsju3KK47wWlXhb1deQ/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1vvGCJsPiv8nnm0NXLB6BRGZYKXfsBHWr/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49919,22 +51210,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>NODA</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
       <c r="G372" s="50" t="n">
-        <v>10.6</v>
+        <v>180</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
@@ -49950,7 +51241,7 @@
         <v>1</v>
       </c>
       <c r="K372" s="50" t="n">
-        <v>10.6</v>
+        <v>180</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -49959,12 +51250,12 @@
       </c>
       <c r="M372" s="52" t="inlineStr">
         <is>
-          <t>838932834</t>
+          <t>160/26</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1sO9yIL4F2nAwRKASwSF6ZpxjuzHEmOc7/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1MjbvGYnouuMkppyPq0weIAEzTe4k5xge/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -49981,26 +51272,30 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>logistics</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>api_usage</t>
+        </is>
+      </c>
       <c r="G373" s="50" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -50009,10 +51304,10 @@
         </is>
       </c>
       <c r="J373" s="51" t="n">
-        <v>1</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="K373" s="50" t="n">
-        <v>5</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -50021,12 +51316,12 @@
       </c>
       <c r="M373" s="52" t="inlineStr">
         <is>
-          <t>838970930</t>
+          <t>1D95DDC40021</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CktdzAiLdEaTGp8PTl1rBwlPK6ofbmCk/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1YmSr3hruJGv95Cte5Hdf3D_wDyE1GdI1/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -50053,12 +51348,16 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>chatgpt_plus</t>
+        </is>
+      </c>
       <c r="G374" s="50" t="n">
-        <v>440</v>
+        <v>85.12</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
@@ -50074,7 +51373,7 @@
         <v>1</v>
       </c>
       <c r="K374" s="50" t="n">
-        <v>440</v>
+        <v>85.12</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -50083,19 +51382,19 @@
       </c>
       <c r="M374" s="52" t="inlineStr">
         <is>
-          <t>OQXBYXMP-0010</t>
+          <t>7BSDV5AM-0004</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1FXNVZoKgHf-kpedRvpbGDRh36qQQk2gb/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1zz5LASlTYsQglYZHAdlobUGBURvgCxBV/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="375" ht="12" customHeight="1">
       <c r="A375" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -50105,22 +51404,26 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr"/>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>chatgpt_plus</t>
+        </is>
+      </c>
       <c r="G375" s="50" t="n">
-        <v>13737</v>
+        <v>19.01</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -50136,20 +51439,28 @@
         <v>1</v>
       </c>
       <c r="K375" s="50" t="n">
-        <v>13737</v>
+        <v>19.01</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M375" t="inlineStr"/>
-      <c r="N375" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M375" s="52" t="inlineStr">
+        <is>
+          <t>HPTYPXYP-0001</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1XiV0belx8HMpXLhBrEEw7NdwOr6W6EpP/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="12" customHeight="1">
       <c r="A376" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -50164,17 +51475,17 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" s="50" t="n">
-        <v>16662</v>
+        <v>2385.5</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -50190,20 +51501,28 @@
         <v>1</v>
       </c>
       <c r="K376" s="50" t="n">
-        <v>16662</v>
+        <v>2385.5</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M376" t="inlineStr"/>
-      <c r="N376" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M376" s="52" t="inlineStr">
+        <is>
+          <t>FAC/2026/26100006968</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Swbg48jkgAhgbOKDvZz6gzEuqHXGoTnM/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="12" customHeight="1">
       <c r="A377" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -50218,17 +51537,17 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>PRESSING</t>
         </is>
       </c>
       <c r="F377" t="inlineStr"/>
       <c r="G377" s="50" t="n">
-        <v>14544</v>
+        <v>29051.19</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -50244,20 +51563,28 @@
         <v>1</v>
       </c>
       <c r="K377" s="50" t="n">
-        <v>14544</v>
+        <v>29051.19</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M377" t="inlineStr"/>
-      <c r="N377" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M377" s="52" t="inlineStr">
+        <is>
+          <t>FAC/2026/26100007066</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sm9nxclqBRqT0Rt8ngNxwkQGhYMy5MY1/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="12" customHeight="1">
       <c r="A378" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -50272,17 +51599,21 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr"/>
+          <t>PRESSING</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
       <c r="G378" s="50" t="n">
-        <v>13605</v>
+        <v>350.41</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -50298,20 +51629,28 @@
         <v>1</v>
       </c>
       <c r="K378" s="50" t="n">
-        <v>13605</v>
+        <v>350.41</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M378" s="52" t="inlineStr">
+        <is>
+          <t>R-2026-0001</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1BgipjaNJok28U6NHH7hb1HzCn7H_8YYR/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="12" customHeight="1">
       <c r="A379" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -50321,22 +51660,22 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" s="50" t="n">
-        <v>13698</v>
+        <v>372.16</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -50352,20 +51691,28 @@
         <v>1</v>
       </c>
       <c r="K379" s="50" t="n">
-        <v>13698</v>
+        <v>372.16</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M379" s="52" t="inlineStr">
+        <is>
+          <t>241860</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rfPfdJcTvizW0eXGbWDtwHLLG8g79BXM/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="12" customHeight="1">
       <c r="A380" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -50375,26 +51722,26 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" s="50" t="n">
-        <v>11562</v>
+        <v>106.52</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -50403,23 +51750,31 @@
         </is>
       </c>
       <c r="J380" s="51" t="n">
-        <v>1</v>
+        <v>0.86542622</v>
       </c>
       <c r="K380" s="50" t="n">
-        <v>11562</v>
+        <v>92.19</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M380" t="inlineStr"/>
-      <c r="N380" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M380" s="52" t="inlineStr">
+        <is>
+          <t>1602C2F5-0025</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1rFPuzyS4ej-RG1TM9N1r7EfA_1IhJb4L/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="12" customHeight="1">
       <c r="A381" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -50434,17 +51789,17 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" s="50" t="n">
-        <v>14731.84</v>
+        <v>256.5</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
@@ -50460,20 +51815,28 @@
         <v>1</v>
       </c>
       <c r="K381" s="50" t="n">
-        <v>14731.84</v>
+        <v>256.5</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M381" t="inlineStr"/>
-      <c r="N381" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M381" s="52" t="inlineStr">
+        <is>
+          <t>RVR-21729</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17YPz8z7fRt7mMpHRe7X63aN95sJfrkid/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="12" customHeight="1">
       <c r="A382" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -50488,17 +51851,17 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" s="50" t="n">
-        <v>14915.68</v>
+        <v>256.5</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
@@ -50514,20 +51877,28 @@
         <v>1</v>
       </c>
       <c r="K382" s="50" t="n">
-        <v>14915.68</v>
+        <v>256.5</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M382" t="inlineStr"/>
-      <c r="N382" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M382" s="52" t="inlineStr">
+        <is>
+          <t>RVR-21873</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1tSGPsHHVzqmLGDRBLKLoeEggwrJqW_6L/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="12" customHeight="1">
       <c r="A383" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -50542,17 +51913,17 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" s="50" t="n">
-        <v>15349.42</v>
+        <v>79</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
@@ -50568,20 +51939,28 @@
         <v>1</v>
       </c>
       <c r="K383" s="50" t="n">
-        <v>15349.42</v>
+        <v>79</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M383" t="inlineStr"/>
-      <c r="N383" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M383" s="52" t="inlineStr">
+        <is>
+          <t>RVR-22332</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1z4saK7F3rxKzXrumdfYopy3wLeFqH0Dt/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="12" customHeight="1">
       <c r="A384" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -50596,21 +51975,21 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" s="50" t="n">
-        <v>15515.1</v>
+        <v>3291.42</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -50619,23 +51998,31 @@
         </is>
       </c>
       <c r="J384" s="51" t="n">
-        <v>1</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="K384" s="50" t="n">
-        <v>15515.1</v>
+        <v>2865.84</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M384" t="inlineStr"/>
-      <c r="N384" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M384" s="52" t="inlineStr">
+        <is>
+          <t>563465757</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12u1CWpL1978NM0H-5y0u3Q9eDkS_FVGw/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="12" customHeight="1">
       <c r="A385" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -50650,17 +52037,17 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>SIMPLYCOM</t>
         </is>
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" s="50" t="n">
-        <v>15515.1</v>
+        <v>0.54</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -50676,20 +52063,28 @@
         <v>1</v>
       </c>
       <c r="K385" s="50" t="n">
-        <v>15515.1</v>
+        <v>0.54</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M385" t="inlineStr"/>
-      <c r="N385" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M385" s="52" t="inlineStr">
+        <is>
+          <t>4727397</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1vWhd7Pa5SP43onRKws4nymWiU7NozmOg/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="12" customHeight="1">
       <c r="A386" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -50704,21 +52099,21 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" s="50" t="n">
-        <v>15421.77</v>
+        <v>24.99</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -50727,18 +52122,26 @@
         </is>
       </c>
       <c r="J386" s="51" t="n">
-        <v>1</v>
+        <v>0.8707009100000001</v>
       </c>
       <c r="K386" s="50" t="n">
-        <v>15421.77</v>
+        <v>21.76</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M386" t="inlineStr"/>
-      <c r="N386" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M386" s="52" t="inlineStr">
+        <is>
+          <t>TADGCDFS-0006</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QWS2ZKVjIM2Bx2gAdVzmPiIpR_5BGxt4/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="12" customHeight="1">
       <c r="A387" t="inlineStr">
@@ -50758,17 +52161,17 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" s="50" t="n">
-        <v>15515.1</v>
+        <v>15</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -50784,20 +52187,28 @@
         <v>1</v>
       </c>
       <c r="K387" s="50" t="n">
-        <v>15515.1</v>
+        <v>15</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M387" t="inlineStr"/>
-      <c r="N387" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M387" s="52" t="inlineStr">
+        <is>
+          <t>7/2781</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1z8NVoi-_e47R6qkIxAaXaFscoze8wk2b/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="12" customHeight="1">
       <c r="A388" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -50807,26 +52218,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Otros gastos enero 2026</t>
-        </is>
-      </c>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
       <c r="G388" s="50" t="n">
-        <v>411.87</v>
+        <v>-569.03</v>
       </c>
       <c r="H388" t="inlineStr">
         <is>
@@ -50842,20 +52249,28 @@
         <v>1</v>
       </c>
       <c r="K388" s="50" t="n">
-        <v>411.87</v>
+        <v>-569.03</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M388" t="inlineStr"/>
-      <c r="N388" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M388" s="52" t="inlineStr">
+        <is>
+          <t>2003660927</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/11-v2MJhXEqPk_yYCx2KlK8ou1Hj1nl96/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="12" customHeight="1">
       <c r="A389" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -50865,26 +52280,22 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>Otros gastos febrero 2026</t>
-        </is>
-      </c>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" s="50" t="n">
-        <v>554.46</v>
+        <v>509.48</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -50900,20 +52311,28 @@
         <v>1</v>
       </c>
       <c r="K389" s="50" t="n">
-        <v>554.46</v>
+        <v>509.48</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M389" t="inlineStr"/>
-      <c r="N389" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M389" s="52" t="inlineStr">
+        <is>
+          <t>327870911</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/16ubitUS_HwiWCAlQIEN9NuPpQ3Kiu4wg/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="12" customHeight="1">
       <c r="A390" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -50923,26 +52342,22 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Gastos no categorizados abril 2026</t>
-        </is>
-      </c>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
       <c r="G390" s="50" t="n">
-        <v>935.45</v>
+        <v>853.66</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
@@ -50958,73 +52373,1755 @@
         <v>1</v>
       </c>
       <c r="K390" s="50" t="n">
-        <v>935.45</v>
+        <v>853.66</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M390" s="52" t="inlineStr">
+        <is>
+          <t>327903065</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1hjw_XrPrz9bJ96OfjFlmMQIFAS8EGuwO/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="12" customHeight="1">
       <c r="A391" t="inlineStr">
         <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" s="50" t="n">
+        <v>1336.55</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J391" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" s="50" t="n">
+        <v>1336.55</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M391" s="52" t="inlineStr">
+        <is>
+          <t>327934792</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1A2tjqFyfnDai7ZyuG3PAxaNkx_P1PrBZ/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="12" customHeight="1">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" s="50" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J392" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K392" s="50" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M392" s="52" t="inlineStr">
+        <is>
+          <t>838889502</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/10MqUF30Ux7n5Fvsju3KK47wWlXhb1deQ/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="12" customHeight="1">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" s="50" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J393" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K393" s="50" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M393" s="52" t="inlineStr">
+        <is>
+          <t>838932834</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1sO9yIL4F2nAwRKASwSF6ZpxjuzHEmOc7/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="12" customHeight="1">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J394" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K394" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M394" s="52" t="inlineStr">
+        <is>
+          <t>838970930</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1CktdzAiLdEaTGp8PTl1rBwlPK6ofbmCk/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="12" customHeight="1">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" s="50" t="n">
+        <v>440</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J395" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K395" s="50" t="n">
+        <v>440</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M395" s="52" t="inlineStr">
+        <is>
+          <t>OQXBYXMP-0010</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1FXNVZoKgHf-kpedRvpbGDRh36qQQk2gb/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="12" customHeight="1">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>APPHOTOES</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" s="50" t="n">
+        <v>4483.5</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J396" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K396" s="50" t="n">
+        <v>4483.5</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M396" s="52" t="inlineStr">
+        <is>
+          <t>1-10059</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1KnflokmOoEcsKbK1cLffnf8ZOqxWlnjd/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="12" customHeight="1">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>APPHOTOES</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" s="50" t="n">
+        <v>3337.4</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J397" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K397" s="50" t="n">
+        <v>3337.4</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M397" s="52" t="inlineStr">
+        <is>
+          <t>1-10069</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17KmrW6uNsc0RjLFoPp80SpUeUTIByW9R/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="12" customHeight="1">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>APPHOTOES</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J398" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K398" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M398" s="52" t="inlineStr">
+        <is>
+          <t>1-9983</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12KZizHp8W6aWRLd41QAeFd0sGH9ARMcv/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="12" customHeight="1">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>BBVACNC</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" s="50" t="n">
+        <v>1644.62</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J399" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K399" s="50" t="n">
+        <v>1644.62</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M399" s="52" t="inlineStr">
+        <is>
+          <t>260992A00367589</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1K0yXzhhYek9UAxW3RV27j1pjSJp0i3WW/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="12" customHeight="1">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>CLARIS</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" s="50" t="n">
+        <v>808.08</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J400" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K400" s="50" t="n">
+        <v>808.08</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M400" s="52" t="inlineStr">
+        <is>
+          <t>F02716/26</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/13RM-86LJmj708bQBMZ5BO7W5j47HU4KI/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="12" customHeight="1">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" s="50" t="n">
+        <v>111.07</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J401" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K401" s="50" t="n">
+        <v>111.07</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M401" s="52" t="inlineStr">
+        <is>
+          <t>RVR-22464</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1au7VshI0RM4MtoRue5AClrxY4yPL64dH/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="12" customHeight="1">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J402" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K402" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M402" s="52" t="inlineStr">
+        <is>
+          <t>7/3096</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HJkenN15mK2054HGwv4o35gMpC0wDJ58/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="12" customHeight="1">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" s="50" t="n">
+        <v>13737</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J403" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K403" s="50" t="n">
+        <v>13737</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+    </row>
+    <row r="404" ht="12" customHeight="1">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" s="50" t="n">
+        <v>16662</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J404" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K404" s="50" t="n">
+        <v>16662</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+    </row>
+    <row r="405" ht="12" customHeight="1">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" s="50" t="n">
+        <v>14544</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J405" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K405" s="50" t="n">
+        <v>14544</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+    </row>
+    <row r="406" ht="12" customHeight="1">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" s="50" t="n">
+        <v>13605</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J406" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K406" s="50" t="n">
+        <v>13605</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
+    </row>
+    <row r="407" ht="12" customHeight="1">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" s="50" t="n">
+        <v>13698</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J407" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K407" s="50" t="n">
+        <v>13698</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+    </row>
+    <row r="408" ht="12" customHeight="1">
+      <c r="A408" t="inlineStr">
+        <is>
           <t>202606</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" s="50" t="n">
+        <v>11562</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J408" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K408" s="50" t="n">
+        <v>11562</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+    </row>
+    <row r="409" ht="12" customHeight="1">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" s="50" t="n">
+        <v>14826</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J409" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K409" s="50" t="n">
+        <v>14826</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+    </row>
+    <row r="410" ht="12" customHeight="1">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" s="50" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J410" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K410" s="50" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+    </row>
+    <row r="411" ht="12" customHeight="1">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" s="50" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J411" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K411" s="50" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+    </row>
+    <row r="412" ht="12" customHeight="1">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" s="50" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J412" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K412" s="50" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
+    </row>
+    <row r="413" ht="12" customHeight="1">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J413" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K413" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+    </row>
+    <row r="414" ht="12" customHeight="1">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J414" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K414" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
+    </row>
+    <row r="415" ht="12" customHeight="1">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" s="50" t="n">
+        <v>15421.77</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J415" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K415" s="50" t="n">
+        <v>15421.77</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
+    </row>
+    <row r="416" ht="12" customHeight="1">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J416" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K416" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+    </row>
+    <row r="417" ht="12" customHeight="1">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr">
+      <c r="E417" t="inlineStr">
         <is>
           <t>OTROSGASTOS</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Otros gastos enero 2026</t>
+        </is>
+      </c>
+      <c r="G417" s="50" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J417" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K417" s="50" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+    </row>
+    <row r="418" ht="12" customHeight="1">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Otros gastos febrero 2026</t>
+        </is>
+      </c>
+      <c r="G418" s="50" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J418" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K418" s="50" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+    </row>
+    <row r="419" ht="12" customHeight="1">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Gastos no categorizados abril 2026</t>
+        </is>
+      </c>
+      <c r="G419" s="50" t="n">
+        <v>935.45</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J419" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K419" s="50" t="n">
+        <v>935.45</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
+    </row>
+    <row r="420" ht="12" customHeight="1">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
         <is>
           <t>Otros gastos junio 2026</t>
         </is>
       </c>
-      <c r="G391" s="50" t="n">
+      <c r="G420" s="50" t="n">
         <v>240.24</v>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J391" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K391" s="50" t="n">
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J420" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K420" s="50" t="n">
         <v>240.24</v>
       </c>
-      <c r="L391" t="inlineStr">
+      <c r="L420" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr"/>
-      <c r="N391" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -51401,6 +54498,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M372" r:id="rId370"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M373" r:id="rId371"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M374" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M375" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M376" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M377" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M378" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M379" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M380" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M381" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M382" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M383" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M384" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M385" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M386" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M387" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M388" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M389" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M390" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M391" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M392" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M393" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M394" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M395" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M396" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M397" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M398" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M399" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId400"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -868,7 +868,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 10/08/2026 23:59 h</t>
+          <t>Shopify daily average | Actualizado: 11/08/2026 00:13 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10T21:59:52Z</t>
+          <t>2026-08-10T22:13:48Z</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="E82" s="50" t="n">
-        <v>19210.62</v>
+        <v>792.85</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="50" t="n">
-        <v>19210.62</v>
+        <v>792.85</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="E84" s="50" t="n">
-        <v>13571.05</v>
+        <v>1737.85</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="50" t="n">
-        <v>13571.05</v>
+        <v>1737.85</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         </is>
       </c>
       <c r="E89" s="50" t="n">
-        <v>11435.23</v>
+        <v>2595.85</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="50" t="n">
-        <v>11435.23</v>
+        <v>2595.85</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         </is>
       </c>
       <c r="E91" s="50" t="n">
-        <v>17609.98</v>
+        <v>1606.98</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="50" t="n">
-        <v>17609.98</v>
+        <v>1606.98</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>

--- a/output/spreadsheet/pyg_sl_2026.xlsx
+++ b/output/spreadsheet/pyg_sl_2026.xlsx
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q136"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -868,7 +868,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 11/08/2026 00:13 h</t>
+          <t>Shopify daily average | Actualizado: 04/09/2026 09:59 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -6171,51 +6171,51 @@
       </c>
       <c r="C84" s="13" t="n"/>
       <c r="D84" s="14">
-        <f>D85+D95+D98+D114+D132</f>
+        <f>D85+D95+D98+D115+D133</f>
         <v/>
       </c>
       <c r="E84" s="14">
-        <f>E85+E95+E98+E114+E132</f>
+        <f>E85+E95+E98+E115+E133</f>
         <v/>
       </c>
       <c r="F84" s="14">
-        <f>F85+F95+F98+F114+F132</f>
+        <f>F85+F95+F98+F115+F133</f>
         <v/>
       </c>
       <c r="G84" s="14">
-        <f>G85+G95+G98+G114+G132</f>
+        <f>G85+G95+G98+G115+G133</f>
         <v/>
       </c>
       <c r="H84" s="14">
-        <f>H85+H95+H98+H114+H132</f>
+        <f>H85+H95+H98+H115+H133</f>
         <v/>
       </c>
       <c r="I84" s="14">
-        <f>I85+I95+I98+I114+I132</f>
+        <f>I85+I95+I98+I115+I133</f>
         <v/>
       </c>
       <c r="J84" s="14">
-        <f>J85+J95+J98+J114+J132</f>
+        <f>J85+J95+J98+J115+J133</f>
         <v/>
       </c>
       <c r="K84" s="14">
-        <f>K85+K95+K98+K114+K132</f>
+        <f>K85+K95+K98+K115+K133</f>
         <v/>
       </c>
       <c r="L84" s="14">
-        <f>L85+L95+L98+L114+L132</f>
+        <f>L85+L95+L98+L115+L133</f>
         <v/>
       </c>
       <c r="M84" s="14">
-        <f>M85+M95+M98+M114+M132</f>
+        <f>M85+M95+M98+M115+M133</f>
         <v/>
       </c>
       <c r="N84" s="14">
-        <f>N85+N95+N98+N114+N132</f>
+        <f>N85+N95+N98+N115+N133</f>
         <v/>
       </c>
       <c r="O84" s="14">
-        <f>O85+O95+O98+O114+O132</f>
+        <f>O85+O95+O98+O115+O133</f>
         <v/>
       </c>
       <c r="P84" s="15">
@@ -7143,51 +7143,51 @@
         </is>
       </c>
       <c r="D98" s="20">
-        <f>D99+D100+D101+D102+D103+D107+D108+D109+D110+D111+D112+D113</f>
+        <f>D99+D100+D101+D102+D103+D107+D108+D109+D110+D111+D112+D113+D114</f>
         <v/>
       </c>
       <c r="E98" s="20">
-        <f>E99+E100+E101+E102+E103+E107+E108+E109+E110+E111+E112+E113</f>
+        <f>E99+E100+E101+E102+E103+E107+E108+E109+E110+E111+E112+E113+E114</f>
         <v/>
       </c>
       <c r="F98" s="20">
-        <f>F99+F100+F101+F102+F103+F107+F108+F109+F110+F111+F112+F113</f>
+        <f>F99+F100+F101+F102+F103+F107+F108+F109+F110+F111+F112+F113+F114</f>
         <v/>
       </c>
       <c r="G98" s="20">
-        <f>G99+G100+G101+G102+G103+G107+G108+G109+G110+G111+G112+G113</f>
+        <f>G99+G100+G101+G102+G103+G107+G108+G109+G110+G111+G112+G113+G114</f>
         <v/>
       </c>
       <c r="H98" s="20">
-        <f>H99+H100+H101+H102+H103+H107+H108+H109+H110+H111+H112+H113</f>
+        <f>H99+H100+H101+H102+H103+H107+H108+H109+H110+H111+H112+H113+H114</f>
         <v/>
       </c>
       <c r="I98" s="20">
-        <f>I99+I100+I101+I102+I103+I107+I108+I109+I110+I111+I112+I113</f>
+        <f>I99+I100+I101+I102+I103+I107+I108+I109+I110+I111+I112+I113+I114</f>
         <v/>
       </c>
       <c r="J98" s="20">
-        <f>J99+J100+J101+J102+J103+J107+J108+J109+J110+J111+J112+J113</f>
+        <f>J99+J100+J101+J102+J103+J107+J108+J109+J110+J111+J112+J113+J114</f>
         <v/>
       </c>
       <c r="K98" s="20">
-        <f>K99+K100+K101+K102+K103+K107+K108+K109+K110+K111+K112+K113</f>
+        <f>K99+K100+K101+K102+K103+K107+K108+K109+K110+K111+K112+K113+K114</f>
         <v/>
       </c>
       <c r="L98" s="20">
-        <f>L99+L100+L101+L102+L103+L107+L108+L109+L110+L111+L112+L113</f>
+        <f>L99+L100+L101+L102+L103+L107+L108+L109+L110+L111+L112+L113+L114</f>
         <v/>
       </c>
       <c r="M98" s="20">
-        <f>M99+M100+M101+M102+M103+M107+M108+M109+M110+M111+M112+M113</f>
+        <f>M99+M100+M101+M102+M103+M107+M108+M109+M110+M111+M112+M113+M114</f>
         <v/>
       </c>
       <c r="N98" s="20">
-        <f>N99+N100+N101+N102+N103+N107+N108+N109+N110+N111+N112+N113</f>
+        <f>N99+N100+N101+N102+N103+N107+N108+N109+N110+N111+N112+N113+N114</f>
         <v/>
       </c>
       <c r="O98" s="20">
-        <f>O99+O100+O101+O102+O103+O107+O108+O109+O110+O111+O112+O113</f>
+        <f>O99+O100+O101+O102+O103+O107+O108+O109+O110+O111+O112+O113+O114</f>
         <v/>
       </c>
       <c r="P98" s="21">
@@ -8043,13 +8043,13 @@
     <row r="111" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REGUS</t>
+          <t xml:space="preserve">            PHOENIX</t>
         </is>
       </c>
       <c r="B111" s="4" t="n"/>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="D111" s="5">
@@ -8113,13 +8113,13 @@
     <row r="112" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A112" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            TORRAS</t>
+          <t xml:space="preserve">            REGUS</t>
         </is>
       </c>
       <c r="B112" s="4" t="n"/>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D112" s="5">
@@ -8180,16 +8180,16 @@
         </is>
       </c>
     </row>
-    <row r="113" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="113" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A113" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            VITALY</t>
+          <t xml:space="preserve">            TORRAS</t>
         </is>
       </c>
       <c r="B113" s="4" t="n"/>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D113" s="5">
@@ -8250,141 +8250,141 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="12" customHeight="1">
-      <c r="A114" s="17" t="inlineStr">
+    <row r="114" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A114" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            VITALY</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>VITALY</t>
+        </is>
+      </c>
+      <c r="D114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="E114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="F114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="G114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="H114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="I114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="J114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="K114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="L114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="M114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="N114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="O114" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"administration",'g-expenses-sl'!$E:$E,$C114)</f>
+        <v/>
+      </c>
+      <c r="P114" s="24">
+        <f>SUM(D114:O114)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="25" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="12" customHeight="1">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">        Technology</t>
         </is>
       </c>
-      <c r="B114" s="18" t="n"/>
-      <c r="C114" s="19" t="inlineStr">
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="19" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D114" s="20">
-        <f>SUM(D115:D131)</f>
-        <v/>
-      </c>
-      <c r="E114" s="20">
-        <f>SUM(E115:E131)</f>
-        <v/>
-      </c>
-      <c r="F114" s="20">
-        <f>SUM(F115:F131)</f>
-        <v/>
-      </c>
-      <c r="G114" s="20">
-        <f>SUM(G115:G131)</f>
-        <v/>
-      </c>
-      <c r="H114" s="20">
-        <f>SUM(H115:H131)</f>
-        <v/>
-      </c>
-      <c r="I114" s="20">
-        <f>SUM(I115:I131)</f>
-        <v/>
-      </c>
-      <c r="J114" s="20">
-        <f>SUM(J115:J131)</f>
-        <v/>
-      </c>
-      <c r="K114" s="20">
-        <f>SUM(K115:K131)</f>
-        <v/>
-      </c>
-      <c r="L114" s="20">
-        <f>SUM(L115:L131)</f>
-        <v/>
-      </c>
-      <c r="M114" s="20">
-        <f>SUM(M115:M131)</f>
-        <v/>
-      </c>
-      <c r="N114" s="20">
-        <f>SUM(N115:N131)</f>
-        <v/>
-      </c>
-      <c r="O114" s="20">
-        <f>SUM(O115:O131)</f>
-        <v/>
-      </c>
-      <c r="P114" s="21">
-        <f>SUM(D114:O114)</f>
-        <v/>
-      </c>
-      <c r="Q114" s="22" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A115" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADOBE</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="E115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="F115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="G115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="H115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="I115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="J115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="K115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="L115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="M115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="N115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="O115" s="5">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C115)</f>
-        <v/>
-      </c>
-      <c r="P115" s="24">
+      <c r="D115" s="20">
+        <f>SUM(D116:D132)</f>
+        <v/>
+      </c>
+      <c r="E115" s="20">
+        <f>SUM(E116:E132)</f>
+        <v/>
+      </c>
+      <c r="F115" s="20">
+        <f>SUM(F116:F132)</f>
+        <v/>
+      </c>
+      <c r="G115" s="20">
+        <f>SUM(G116:G132)</f>
+        <v/>
+      </c>
+      <c r="H115" s="20">
+        <f>SUM(H116:H132)</f>
+        <v/>
+      </c>
+      <c r="I115" s="20">
+        <f>SUM(I116:I132)</f>
+        <v/>
+      </c>
+      <c r="J115" s="20">
+        <f>SUM(J116:J132)</f>
+        <v/>
+      </c>
+      <c r="K115" s="20">
+        <f>SUM(K116:K132)</f>
+        <v/>
+      </c>
+      <c r="L115" s="20">
+        <f>SUM(L116:L132)</f>
+        <v/>
+      </c>
+      <c r="M115" s="20">
+        <f>SUM(M116:M132)</f>
+        <v/>
+      </c>
+      <c r="N115" s="20">
+        <f>SUM(N116:N132)</f>
+        <v/>
+      </c>
+      <c r="O115" s="20">
+        <f>SUM(O116:O132)</f>
+        <v/>
+      </c>
+      <c r="P115" s="21">
         <f>SUM(D115:O115)</f>
         <v/>
       </c>
-      <c r="Q115" s="25" t="inlineStr">
+      <c r="Q115" s="22" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -8393,13 +8393,13 @@
     <row r="116" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A116" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            CANVA</t>
+          <t xml:space="preserve">            ADOBE</t>
         </is>
       </c>
       <c r="B116" s="4" t="n"/>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D116" s="5">
@@ -8463,13 +8463,13 @@
     <row r="117" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A117" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GODADDY</t>
+          <t xml:space="preserve">            CANVA</t>
         </is>
       </c>
       <c r="B117" s="4" t="n"/>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D117" s="5">
@@ -8533,13 +8533,13 @@
     <row r="118" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A118" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
+          <t xml:space="preserve">            GODADDY</t>
         </is>
       </c>
       <c r="B118" s="4" t="n"/>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D118" s="5">
@@ -8603,13 +8603,13 @@
     <row r="119" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A119" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            GORGIAS</t>
+          <t xml:space="preserve">            GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B119" s="4" t="n"/>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D119" s="5">
@@ -8673,13 +8673,13 @@
     <row r="120" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            HETZNER</t>
+          <t xml:space="preserve">            GORGIAS</t>
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D120" s="5">
@@ -8743,13 +8743,13 @@
     <row r="121" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            KONVOAI</t>
+          <t xml:space="preserve">            HETZNER</t>
         </is>
       </c>
       <c r="B121" s="4" t="n"/>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D121" s="5">
@@ -8813,13 +8813,13 @@
     <row r="122" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MASMOVIL</t>
+          <t xml:space="preserve">            KONVOAI</t>
         </is>
       </c>
       <c r="B122" s="4" t="n"/>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D122" s="5">
@@ -8883,13 +8883,13 @@
     <row r="123" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            MICROSOFT</t>
+          <t xml:space="preserve">            MASMOVIL</t>
         </is>
       </c>
       <c r="B123" s="4" t="n"/>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D123" s="5">
@@ -8953,13 +8953,13 @@
     <row r="124" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A124" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            OPENAI</t>
+          <t xml:space="preserve">            MICROSOFT</t>
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D124" s="5">
@@ -9023,13 +9023,13 @@
     <row r="125" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A125" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            PRODUCTHERO</t>
+          <t xml:space="preserve">            OPENAI</t>
         </is>
       </c>
       <c r="B125" s="4" t="n"/>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D125" s="5">
@@ -9093,13 +9093,13 @@
     <row r="126" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A126" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            RAILWAY</t>
+          <t xml:space="preserve">            PRODUCTHERO</t>
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D126" s="5">
@@ -9163,13 +9163,13 @@
     <row r="127" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A127" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            REVER</t>
+          <t xml:space="preserve">            RAILWAY</t>
         </is>
       </c>
       <c r="B127" s="4" t="n"/>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D127" s="5">
@@ -9233,13 +9233,13 @@
     <row r="128" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A128" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SHOPIFY</t>
+          <t xml:space="preserve">            REVER</t>
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D128" s="5">
@@ -9303,13 +9303,13 @@
     <row r="129" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A129" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SIMPLYCOM</t>
+          <t xml:space="preserve">            SHOPIFY</t>
         </is>
       </c>
       <c r="B129" s="4" t="n"/>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>SIMPLYCOM</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D129" s="5">
@@ -9373,13 +9373,13 @@
     <row r="130" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A130" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            SYNCWITH</t>
+          <t xml:space="preserve">            SIMPLYCOM</t>
         </is>
       </c>
       <c r="B130" s="4" t="n"/>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SIMPLYCOM</t>
         </is>
       </c>
       <c r="D130" s="5">
@@ -9440,16 +9440,16 @@
         </is>
       </c>
     </row>
-    <row r="131" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+    <row r="131" hidden="1" outlineLevel="1" ht="12" customHeight="1">
       <c r="A131" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">            YUMAAI</t>
+          <t xml:space="preserve">            SYNCWITH</t>
         </is>
       </c>
       <c r="B131" s="4" t="n"/>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="D131" s="5">
@@ -9510,71 +9510,71 @@
         </is>
       </c>
     </row>
-    <row r="132" ht="12" customHeight="1">
-      <c r="A132" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="B132" s="18" t="n"/>
-      <c r="C132" s="19" t="inlineStr">
-        <is>
-          <t>Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="D132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O132" s="20">
-        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P132" s="21">
+    <row r="132" hidden="1" outlineLevel="1" collapsed="1" ht="12" customHeight="1">
+      <c r="A132" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            YUMAAI</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="D132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="E132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="F132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="G132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="H132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="I132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="J132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="K132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="L132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="M132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="N132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="O132" s="5">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"technology",'g-expenses-sl'!$E:$E,$C132)</f>
+        <v/>
+      </c>
+      <c r="P132" s="24">
         <f>SUM(D132:O132)</f>
         <v/>
       </c>
-      <c r="Q132" s="22" t="inlineStr">
+      <c r="Q132" s="25" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -9583,186 +9583,256 @@
     <row r="133" ht="12" customHeight="1">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="B133" s="19" t="inlineStr">
-        <is>
-          <t>Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="20" t="n">
-        <v>-132.9</v>
-      </c>
-      <c r="E133" s="20" t="n">
-        <v>-277.52</v>
-      </c>
-      <c r="F133" s="20" t="n"/>
-      <c r="G133" s="20" t="n">
-        <v>140.18</v>
-      </c>
-      <c r="H133" s="20" t="n"/>
-      <c r="I133" s="20" t="n">
-        <v>261.71</v>
-      </c>
-      <c r="J133" s="20" t="n"/>
-      <c r="K133" s="20" t="n"/>
-      <c r="L133" s="20" t="n"/>
-      <c r="M133" s="20" t="n"/>
-      <c r="N133" s="20" t="n"/>
-      <c r="O133" s="20" t="n"/>
+          <t xml:space="preserve">        Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="n"/>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
+      <c r="D133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,D$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,E$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,F$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,G$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,H$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,I$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,J$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,K$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,L$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,M$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,N$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O133" s="20">
+        <f>SUMIFS('g-expenses-sl'!$K:$K,'g-expenses-sl'!$A:$A,O$1,'g-expenses-sl'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P133" s="21">
         <f>SUM(D133:O133)</f>
         <v/>
       </c>
-      <c r="Q133" s="30" t="n"/>
+      <c r="Q133" s="22" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="12" customHeight="1">
-      <c r="A134" s="4" t="n"/>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="5" t="n"/>
-      <c r="E134" s="5" t="n"/>
-      <c r="F134" s="5" t="n"/>
-      <c r="G134" s="5" t="n"/>
-      <c r="H134" s="5" t="n"/>
-      <c r="I134" s="5" t="n"/>
-      <c r="J134" s="5" t="n"/>
-      <c r="K134" s="5" t="n"/>
-      <c r="L134" s="5" t="n"/>
-      <c r="M134" s="5" t="n"/>
-      <c r="N134" s="5" t="n"/>
-      <c r="O134" s="5" t="n"/>
-      <c r="P134" s="24">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B134" s="19" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="n"/>
+      <c r="D134" s="20" t="n">
+        <v>-132.9</v>
+      </c>
+      <c r="E134" s="20" t="n">
+        <v>-277.52</v>
+      </c>
+      <c r="F134" s="20" t="n"/>
+      <c r="G134" s="20" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="H134" s="20" t="n"/>
+      <c r="I134" s="20" t="n">
+        <v>261.71</v>
+      </c>
+      <c r="J134" s="20" t="n"/>
+      <c r="K134" s="20" t="n"/>
+      <c r="L134" s="20" t="n"/>
+      <c r="M134" s="20" t="n"/>
+      <c r="N134" s="20" t="n"/>
+      <c r="O134" s="20" t="n"/>
+      <c r="P134" s="21">
         <f>SUM(D134:O134)</f>
         <v/>
       </c>
-      <c r="Q134" s="5" t="n"/>
+      <c r="Q134" s="30" t="n"/>
     </row>
     <row r="135" ht="12" customHeight="1">
-      <c r="A135" s="36" t="inlineStr">
+      <c r="A135" s="4" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="5" t="n"/>
+      <c r="F135" s="5" t="n"/>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
+      <c r="I135" s="5" t="n"/>
+      <c r="J135" s="5" t="n"/>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="5" t="n"/>
+      <c r="N135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="24">
+        <f>SUM(D135:O135)</f>
+        <v/>
+      </c>
+      <c r="Q135" s="5" t="n"/>
+    </row>
+    <row r="136" ht="12" customHeight="1">
+      <c r="A136" s="36" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B135" s="37" t="n"/>
-      <c r="C135" s="37" t="n"/>
-      <c r="D135" s="38">
-        <f>D4-D53-D84-D133</f>
-        <v/>
-      </c>
-      <c r="E135" s="38">
-        <f>E4-E53-E84-E133</f>
-        <v/>
-      </c>
-      <c r="F135" s="38">
-        <f>F4-F53-F84-F133</f>
-        <v/>
-      </c>
-      <c r="G135" s="38">
-        <f>G4-G53-G84-G133</f>
-        <v/>
-      </c>
-      <c r="H135" s="38">
-        <f>H4-H53-H84-H133</f>
-        <v/>
-      </c>
-      <c r="I135" s="38">
-        <f>I4-I53-I84-I133</f>
-        <v/>
-      </c>
-      <c r="J135" s="38">
-        <f>J4-J53-J84-J133</f>
-        <v/>
-      </c>
-      <c r="K135" s="38">
-        <f>K4-K53-K84-K133</f>
-        <v/>
-      </c>
-      <c r="L135" s="38">
-        <f>L4-L53-L84-L133</f>
-        <v/>
-      </c>
-      <c r="M135" s="38">
-        <f>M4-M53-M84-M133</f>
-        <v/>
-      </c>
-      <c r="N135" s="38">
-        <f>N4-N53-N84-N133</f>
-        <v/>
-      </c>
-      <c r="O135" s="38">
-        <f>O4-O53-O84-O133</f>
-        <v/>
-      </c>
-      <c r="P135" s="9">
-        <f>SUM(D135:O135)</f>
-        <v/>
-      </c>
-      <c r="Q135" s="39" t="n"/>
-    </row>
-    <row r="136" ht="12" customHeight="1">
-      <c r="A136" s="40" t="inlineStr">
+      <c r="B136" s="37" t="n"/>
+      <c r="C136" s="37" t="n"/>
+      <c r="D136" s="38">
+        <f>D4-D53-D84-D134</f>
+        <v/>
+      </c>
+      <c r="E136" s="38">
+        <f>E4-E53-E84-E134</f>
+        <v/>
+      </c>
+      <c r="F136" s="38">
+        <f>F4-F53-F84-F134</f>
+        <v/>
+      </c>
+      <c r="G136" s="38">
+        <f>G4-G53-G84-G134</f>
+        <v/>
+      </c>
+      <c r="H136" s="38">
+        <f>H4-H53-H84-H134</f>
+        <v/>
+      </c>
+      <c r="I136" s="38">
+        <f>I4-I53-I84-I134</f>
+        <v/>
+      </c>
+      <c r="J136" s="38">
+        <f>J4-J53-J84-J134</f>
+        <v/>
+      </c>
+      <c r="K136" s="38">
+        <f>K4-K53-K84-K134</f>
+        <v/>
+      </c>
+      <c r="L136" s="38">
+        <f>L4-L53-L84-L134</f>
+        <v/>
+      </c>
+      <c r="M136" s="38">
+        <f>M4-M53-M84-M134</f>
+        <v/>
+      </c>
+      <c r="N136" s="38">
+        <f>N4-N53-N84-N134</f>
+        <v/>
+      </c>
+      <c r="O136" s="38">
+        <f>O4-O53-O84-O134</f>
+        <v/>
+      </c>
+      <c r="P136" s="9">
+        <f>SUM(D136:O136)</f>
+        <v/>
+      </c>
+      <c r="Q136" s="39" t="n"/>
+    </row>
+    <row r="137" ht="12" customHeight="1">
+      <c r="A137" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">        % profit / product sales</t>
         </is>
       </c>
-      <c r="B136" s="41" t="n"/>
-      <c r="C136" s="41" t="n"/>
-      <c r="D136" s="42">
-        <f>IFERROR(D135/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E136" s="42">
-        <f>IFERROR(E135/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F136" s="42">
-        <f>IFERROR(F135/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G136" s="42">
-        <f>IFERROR(G135/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H136" s="42">
-        <f>IFERROR(H135/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I136" s="42">
-        <f>IFERROR(I135/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J136" s="42">
-        <f>IFERROR(J135/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K136" s="42">
-        <f>IFERROR(K135/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L136" s="42">
-        <f>IFERROR(L135/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M136" s="42">
-        <f>IFERROR(M135/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N136" s="42">
-        <f>IFERROR(N135/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O136" s="42">
-        <f>IFERROR(O135/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P136" s="43">
-        <f>IFERROR(P135/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q136" s="34" t="n"/>
+      <c r="B137" s="41" t="n"/>
+      <c r="C137" s="41" t="n"/>
+      <c r="D137" s="42">
+        <f>IFERROR(D136/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E137" s="42">
+        <f>IFERROR(E136/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F137" s="42">
+        <f>IFERROR(F136/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G137" s="42">
+        <f>IFERROR(G136/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H137" s="42">
+        <f>IFERROR(H136/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I137" s="42">
+        <f>IFERROR(I136/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J137" s="42">
+        <f>IFERROR(J136/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K137" s="42">
+        <f>IFERROR(K136/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L137" s="42">
+        <f>IFERROR(L136/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M137" s="42">
+        <f>IFERROR(M136/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N137" s="42">
+        <f>IFERROR(N136/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O137" s="42">
+        <f>IFERROR(O136/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P137" s="43">
+        <f>IFERROR(P136/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q137" s="34" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9863,6 +9933,7 @@
     <hyperlink ref="Q130" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q131" location="'g-expenses-sl'!A1" display="-&gt;"/>
     <hyperlink ref="Q132" location="'g-expenses-sl'!A1" display="-&gt;"/>
+    <hyperlink ref="Q133" location="'g-expenses-sl'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9874,7 +9945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10587,10 +10658,10 @@
         </is>
       </c>
       <c r="G18" s="51" t="n">
-        <v>0.04123371</v>
+        <v>0.04145593</v>
       </c>
       <c r="H18" s="50" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -10615,7 +10686,7 @@
         </is>
       </c>
       <c r="D19" s="50" t="n">
-        <v>473.25</v>
+        <v>1440.01</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -10631,7 +10702,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="50" t="n">
-        <v>473.25</v>
+        <v>1440.01</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -10656,7 +10727,7 @@
         </is>
       </c>
       <c r="D20" s="50" t="n">
-        <v>1193.23</v>
+        <v>3979.37</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -10672,7 +10743,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="50" t="n">
-        <v>1193.23</v>
+        <v>3979.37</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -10710,12 +10781,94 @@
         </is>
       </c>
       <c r="G21" s="51" t="n">
-        <v>0.09119511</v>
+        <v>0.09000900000000001</v>
       </c>
       <c r="H21" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="12" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PAYPAL</t>
+        </is>
+      </c>
+      <c r="D22" s="50" t="n">
+        <v>197.71</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="50" t="n">
+        <v>197.71</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>payment_fee_monthly_summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="12" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SHOPIFY</t>
+        </is>
+      </c>
+      <c r="D23" s="50" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="50" t="n">
+        <v>448.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>payment_fee_monthly_summary</t>
         </is>
@@ -10735,7 +10888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11525,7 +11678,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11539,10 +11692,10 @@
         </is>
       </c>
       <c r="E25" s="51" t="n">
-        <v>24.252</v>
+        <v>24.122</v>
       </c>
       <c r="F25" s="51" t="n">
-        <v>0.04123371</v>
+        <v>0.04145593</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -11591,7 +11744,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11605,10 +11758,10 @@
         </is>
       </c>
       <c r="E27" s="51" t="n">
-        <v>0.85565</v>
+        <v>0.85648</v>
       </c>
       <c r="F27" s="51" t="n">
-        <v>1.16870216</v>
+        <v>1.16756959</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -11624,7 +11777,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11638,10 +11791,10 @@
         </is>
       </c>
       <c r="E28" s="51" t="n">
-        <v>10.9655</v>
+        <v>11.11</v>
       </c>
       <c r="F28" s="51" t="n">
-        <v>0.09119511</v>
+        <v>0.09000900000000001</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -11657,7 +11810,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11671,10 +11824,10 @@
         </is>
       </c>
       <c r="E29" s="51" t="n">
-        <v>1.1555</v>
+        <v>1.1596</v>
       </c>
       <c r="F29" s="51" t="n">
-        <v>0.86542622</v>
+        <v>0.86236633</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -11690,12 +11843,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11704,14 +11857,14 @@
         </is>
       </c>
       <c r="E30" s="51" t="n">
-        <v>0.85565</v>
+        <v>1</v>
       </c>
       <c r="F30" s="51" t="n">
-        <v>1.16870216</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+          <t>identity</t>
         </is>
       </c>
     </row>
@@ -11723,12 +11876,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11737,31 +11890,31 @@
         </is>
       </c>
       <c r="E31" s="51" t="n">
-        <v>1.1555</v>
+        <v>0.86055</v>
       </c>
       <c r="F31" s="51" t="n">
-        <v>0.86542622</v>
+        <v>1.16204753</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202609)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
     <row r="32" ht="12" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>202610</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -11770,14 +11923,14 @@
         </is>
       </c>
       <c r="E32" s="51" t="n">
-        <v>0.85565</v>
+        <v>1.1615</v>
       </c>
       <c r="F32" s="51" t="n">
-        <v>1.16870216</v>
+        <v>0.86095566</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml</t>
         </is>
       </c>
     </row>
@@ -11789,12 +11942,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -11803,10 +11956,10 @@
         </is>
       </c>
       <c r="E33" s="51" t="n">
-        <v>1.1555</v>
+        <v>0.86055</v>
       </c>
       <c r="F33" s="51" t="n">
-        <v>0.86542622</v>
+        <v>1.16204753</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -11817,17 +11970,17 @@
     <row r="34" ht="12" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -11836,14 +11989,14 @@
         </is>
       </c>
       <c r="E34" s="51" t="n">
-        <v>0.85565</v>
+        <v>1.1615</v>
       </c>
       <c r="F34" s="51" t="n">
-        <v>1.16870216</v>
+        <v>0.86095566</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202610)</t>
         </is>
       </c>
     </row>
@@ -11855,12 +12008,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -11869,10 +12022,10 @@
         </is>
       </c>
       <c r="E35" s="51" t="n">
-        <v>1.1555</v>
+        <v>0.86055</v>
       </c>
       <c r="F35" s="51" t="n">
-        <v>0.86542622</v>
+        <v>1.16204753</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -11883,17 +12036,17 @@
     <row r="36" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>202612</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11902,14 +12055,14 @@
         </is>
       </c>
       <c r="E36" s="51" t="n">
-        <v>0.85565</v>
+        <v>1.1615</v>
       </c>
       <c r="F36" s="51" t="n">
-        <v>1.16870216</v>
+        <v>0.86095566</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202611)</t>
         </is>
       </c>
     </row>
@@ -11921,26 +12074,59 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E37" s="51" t="n">
+        <v>0.86055</v>
+      </c>
+      <c r="F37" s="51" t="n">
+        <v>1.16204753</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="12" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>202612</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="E37" s="51" t="n">
-        <v>1.1555</v>
-      </c>
-      <c r="F37" s="51" t="n">
-        <v>0.86542622</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="n">
+        <v>1.1615</v>
+      </c>
+      <c r="F38" s="51" t="n">
+        <v>0.86095566</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.ecb.europa.eu/stats/eurofxref/eurofxref-hist.xml (latest available, no ECB data for 202612)</t>
         </is>
@@ -11960,7 +12146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12523,17 +12709,17 @@
     <row r="23" ht="12" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>regus</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12541,22 +12727,26 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Office cleaning services</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>regus</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12569,17 +12759,17 @@
     <row r="25" ht="12" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VITALY</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>TORRAS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -12587,49 +12777,49 @@
           <t>expenses/opex/administration</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Annual prevention and occupational health service</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GOOGLEADS</t>
+          <t>VITALY</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>expenses/opex/marketing</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>expenses/opex/administration</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Annual prevention and occupational health service</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="12" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>METAADS</t>
+          <t>GOOGLEADS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -12642,67 +12832,67 @@
     <row r="28" ht="12" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DOSCONSULTING</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nóminas</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>expenses/opex/staff</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Monthly payroll management for SL</t>
-        </is>
-      </c>
+          <t>expenses/opex/marketing</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29" ht="12" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>DOSCONSULTING</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ADOBE</t>
+          <t>Nóminas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>expenses/opex/technology</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>expenses/opex/staff</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Monthly payroll management for SL</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="12" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>canva</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -12715,17 +12905,17 @@
     <row r="31" ht="12" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>godaddy</t>
+          <t>canva</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12738,17 +12928,17 @@
     <row r="32" ht="12" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>godaddy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12761,17 +12951,17 @@
     <row r="33" ht="12" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gorgias</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12784,17 +12974,17 @@
     <row r="34" ht="12" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>Gorgias</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12807,17 +12997,17 @@
     <row r="35" ht="12" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>konvo</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -12830,17 +13020,17 @@
     <row r="36" ht="12" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mas movil</t>
+          <t>konvo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -12853,17 +13043,17 @@
     <row r="37" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>mas movil</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -12876,17 +13066,17 @@
     <row r="38" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>chatgpt</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -12894,26 +13084,22 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Groups ChatGPT and API</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39" ht="12" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ProductHERO</t>
+          <t>chatgpt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -12921,22 +13107,26 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Groups ChatGPT and API</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>ProductHERO</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -12949,17 +13139,17 @@
     <row r="41" ht="12" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -12972,17 +13162,17 @@
     <row r="42" ht="12" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -12995,17 +13185,17 @@
     <row r="43" ht="12" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SIMPLYCOM</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SIMPLYCOM</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SimplyCom</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -13013,26 +13203,22 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Domain and DNS services</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44" ht="12" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SIMPLYCOM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SIMPLYCOM</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SyncWith</t>
+          <t>SimplyCom</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -13042,24 +13228,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monthly subscription invoiced one month in arrears</t>
+          <t>Domain and DNS services</t>
         </is>
       </c>
     </row>
     <row r="45" ht="12" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>YUMAAI</t>
+          <t>SYNCWITH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YUMA</t>
+          <t>SyncWith</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -13067,76 +13253,76 @@
           <t>expenses/opex/technology</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Monthly subscription invoiced one month in arrears</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="12" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LIVITUM</t>
+          <t>YUMAAI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>709. Rappels</t>
+          <t>YUMA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>income/other_income/rappels</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Rappel issued to Livitum</t>
-        </is>
-      </c>
+          <t>expenses/opex/technology</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47" ht="12" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>LIVITUM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHOOSE</t>
+          <t>709. Rappels</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>income/sales/marketplaces</t>
+          <t>income/other_income/rappels</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Outgoing partner invoice</t>
+          <t>Rappel issued to Livitum</t>
         </is>
       </c>
     </row>
     <row r="48" ht="12" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MAISONS</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MAISONS</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Maisons du Monde</t>
+          <t>CHOOSE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -13146,24 +13332,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marketplace commissions and subscription invoices shown as negative marketplace revenue</t>
+          <t>Outgoing partner invoice</t>
         </is>
       </c>
     </row>
     <row r="49" ht="12" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>MAISONS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>MAISONS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TOASTY</t>
+          <t>Maisons du Monde</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -13173,32 +13359,59 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Outgoing partner invoice</t>
+          <t>Marketplace commissions and subscription invoices shown as negative marketplace revenue</t>
         </is>
       </c>
     </row>
     <row r="50" ht="12" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TOASTY</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>income/sales/marketplaces</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Outgoing partner invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="12" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>QHANDS</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>income/shared-services</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Outgoing CNC rental invoice</t>
         </is>
@@ -13218,7 +13431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13358,22 +13571,22 @@
     <row r="10" ht="12" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>eu</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1272</v>
+        <v>15219</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -13382,13 +13595,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1596</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -13397,13 +13610,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1938</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13412,13 +13625,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1617</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13427,13 +13640,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1629</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202605</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13442,13 +13655,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1767</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202606</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13457,43 +13670,43 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1692</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202607</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>471</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>744</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -13502,13 +13715,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>741</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202602</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -13517,13 +13730,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>567</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202603</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -13532,13 +13745,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>471</v>
+        <v>741</v>
       </c>
     </row>
     <row r="22" ht="12" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202604</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -13547,22 +13760,67 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>543</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" ht="12" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="24" ht="12" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="25" ht="12" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>202607</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>us</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C25" t="n">
         <v>498</v>
+      </c>
+    </row>
+    <row r="26" ht="12" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -13579,7 +13837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q110"/>
+  <dimension ref="A1:Q111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13774,10 +14032,10 @@
         <v>19</v>
       </c>
       <c r="K4" s="54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L4" s="54" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M4" s="54" t="n">
         <v>0</v>
@@ -13789,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="P4" s="54" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="Q4" s="54" t="n"/>
     </row>
@@ -13823,10 +14081,10 @@
         <v>15</v>
       </c>
       <c r="K5" s="55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L5" s="55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M5" s="55" t="n">
         <v>0</v>
@@ -13838,7 +14096,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="55" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="Q5" s="55" t="n"/>
     </row>
@@ -13872,10 +14130,10 @@
         <v>14</v>
       </c>
       <c r="K6" s="57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L6" s="57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M6" s="57" t="n">
         <v>0</v>
@@ -13887,7 +14145,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="57" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="57" t="n"/>
     </row>
@@ -13922,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -13934,7 +14192,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
@@ -13968,7 +14226,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -13980,7 +14238,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -14014,7 +14272,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -14026,7 +14284,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" ht="12" customHeight="1">
@@ -14060,7 +14318,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -14072,7 +14330,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" ht="12" customHeight="1">
@@ -14106,7 +14364,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -14118,7 +14376,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="12" customHeight="1">
@@ -14152,7 +14410,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -14164,7 +14422,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1">
@@ -14198,7 +14456,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -14210,7 +14468,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1">
@@ -14244,7 +14502,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -14256,7 +14514,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" ht="12" customHeight="1">
@@ -14290,7 +14548,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -14302,7 +14560,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
@@ -14336,7 +14594,7 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -14348,7 +14606,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="12" customHeight="1">
@@ -14378,10 +14636,10 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
@@ -14394,7 +14652,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
@@ -14424,11 +14682,11 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="59" t="n">
-        <v>0</v>
+      <c r="K18" t="n">
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14440,7 +14698,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" ht="12" customHeight="1">
@@ -14474,7 +14732,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14486,7 +14744,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="12" customHeight="1">
@@ -14520,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14532,7 +14790,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" ht="12" customHeight="1">
@@ -14611,7 +14869,7 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="59" t="n">
+      <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
@@ -15035,7 +15293,7 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" s="59" t="n">
+      <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
@@ -15081,7 +15339,7 @@
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" s="59" t="n">
+      <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
@@ -15127,7 +15385,7 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="59" t="n">
+      <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
@@ -15173,7 +15431,7 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" s="59" t="n">
+      <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
@@ -15272,10 +15530,10 @@
         <v>49</v>
       </c>
       <c r="K38" s="54" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="L38" s="54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="54" t="n">
         <v>0</v>
@@ -15287,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="54" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="Q38" s="54" t="n"/>
     </row>
@@ -15321,10 +15579,10 @@
         <v>25</v>
       </c>
       <c r="K39" s="55" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L39" s="55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="55" t="n">
         <v>0</v>
@@ -15336,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="55" t="n">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="Q39" s="55" t="n"/>
     </row>
@@ -15370,7 +15628,7 @@
         <v>12</v>
       </c>
       <c r="K40" s="57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L40" s="57" t="n">
         <v>0</v>
@@ -15385,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="57" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q40" s="57" t="n"/>
     </row>
@@ -15416,7 +15674,7 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="59" t="n">
+      <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
@@ -15465,7 +15723,7 @@
       <c r="K42" t="n">
         <v>3</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
@@ -15554,10 +15812,10 @@
       <c r="J44" t="n">
         <v>3</v>
       </c>
-      <c r="K44" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
@@ -15570,7 +15828,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" ht="12" customHeight="1">
@@ -15600,10 +15858,10 @@
       <c r="J45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
@@ -15616,7 +15874,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="12" customHeight="1">
@@ -15649,7 +15907,7 @@
         <v>10</v>
       </c>
       <c r="K46" s="57" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L46" s="57" t="n">
         <v>0</v>
@@ -15664,7 +15922,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="57" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Q46" s="57" t="n"/>
     </row>
@@ -15695,10 +15953,10 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
@@ -15711,7 +15969,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" ht="12" customHeight="1">
@@ -15741,10 +15999,10 @@
       <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
@@ -15757,7 +16015,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" ht="12" customHeight="1">
@@ -15787,7 +16045,7 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" s="59" t="n">
+      <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
@@ -15879,10 +16137,10 @@
       <c r="J51" t="n">
         <v>7</v>
       </c>
-      <c r="K51" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
+      <c r="K51" t="n">
+        <v>7</v>
+      </c>
+      <c r="L51" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
@@ -15895,7 +16153,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" ht="12" customHeight="1">
@@ -15928,7 +16186,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="57" t="n">
         <v>0</v>
@@ -15943,7 +16201,7 @@
         <v>0</v>
       </c>
       <c r="P52" s="57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q52" s="57" t="n"/>
     </row>
@@ -15974,10 +16232,10 @@
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
@@ -15990,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" ht="12" customHeight="1">
@@ -16020,10 +16278,10 @@
       <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
@@ -16036,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" ht="12" customHeight="1">
@@ -16066,10 +16324,10 @@
       <c r="J55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
@@ -16082,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" ht="12" customHeight="1">
@@ -16112,10 +16370,10 @@
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
@@ -16128,7 +16386,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" ht="12" customHeight="1">
@@ -16164,7 +16422,7 @@
         <v>4</v>
       </c>
       <c r="L57" s="57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="57" t="n">
         <v>0</v>
@@ -16176,7 +16434,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="57" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q57" s="57" t="n"/>
     </row>
@@ -16211,7 +16469,7 @@
         <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -16223,7 +16481,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" ht="12" customHeight="1">
@@ -16257,7 +16515,7 @@
         <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -16269,7 +16527,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" ht="12" customHeight="1"/>
@@ -16304,10 +16562,10 @@
         <v>24</v>
       </c>
       <c r="K62" s="55" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="L62" s="55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="55" t="n">
         <v>0</v>
@@ -16319,7 +16577,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="55" t="n">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="Q62" s="55" t="n"/>
     </row>
@@ -16776,7 +17034,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="57" t="n">
         <v>0</v>
@@ -16791,7 +17049,7 @@
         <v>0</v>
       </c>
       <c r="P72" s="57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q72" s="57" t="n"/>
     </row>
@@ -16822,10 +17080,10 @@
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
@@ -16838,7 +17096,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1">
@@ -16917,7 +17175,7 @@
         <v>2</v>
       </c>
       <c r="K75" s="57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="57" t="n">
         <v>0</v>
@@ -16932,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="57" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q75" s="57" t="n"/>
     </row>
@@ -17012,7 +17270,7 @@
       <c r="K77" t="n">
         <v>1</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
@@ -17058,7 +17316,7 @@
       <c r="K78" t="n">
         <v>1</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
@@ -17148,7 +17406,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -17163,7 +17421,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" ht="12" customHeight="1">
@@ -17193,10 +17451,10 @@
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
@@ -17209,7 +17467,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" ht="12" customHeight="1">
@@ -17239,10 +17497,10 @@
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M82" t="n">
@@ -17255,7 +17513,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" ht="12" customHeight="1">
@@ -17423,7 +17681,7 @@
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" s="59" t="n">
+      <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
@@ -17491,7 +17749,7 @@
     <row r="88" ht="12" customHeight="1">
       <c r="C88" t="inlineStr">
         <is>
-          <t>REGUS</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -17519,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -17531,38 +17789,38 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" ht="12" customHeight="1">
       <c r="C89" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>REGUS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17577,154 +17835,154 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="12" customHeight="1">
       <c r="C90" t="inlineStr">
         <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" ht="12" customHeight="1">
+      <c r="C91" t="inlineStr">
+        <is>
           <t>VITALY</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" ht="12" customHeight="1">
-      <c r="A91" s="57" t="n"/>
-      <c r="B91" s="57" t="n"/>
-      <c r="C91" s="58" t="inlineStr">
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" ht="12" customHeight="1">
+      <c r="A92" s="57" t="n"/>
+      <c r="B92" s="57" t="n"/>
+      <c r="C92" s="58" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D91" s="57" t="n">
+      <c r="D92" s="57" t="n">
         <v>20</v>
       </c>
-      <c r="E91" s="57" t="n">
+      <c r="E92" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="F91" s="57" t="n">
+      <c r="F92" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="G91" s="57" t="n">
+      <c r="G92" s="57" t="n">
         <v>21</v>
       </c>
-      <c r="H91" s="57" t="n">
+      <c r="H92" s="57" t="n">
         <v>22</v>
       </c>
-      <c r="I91" s="57" t="n">
+      <c r="I92" s="57" t="n">
         <v>28</v>
       </c>
-      <c r="J91" s="57" t="n">
+      <c r="J92" s="57" t="n">
         <v>21</v>
       </c>
-      <c r="K91" s="57" t="n">
-        <v>2</v>
-      </c>
-      <c r="L91" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" s="57" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q91" s="57" t="n"/>
-    </row>
-    <row r="92" ht="12" customHeight="1">
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>ADOBE</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>6</v>
-      </c>
+      <c r="K92" s="57" t="n">
+        <v>16</v>
+      </c>
+      <c r="L92" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="57" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q92" s="57" t="n"/>
     </row>
     <row r="93" ht="12" customHeight="1">
       <c r="C93" t="inlineStr">
         <is>
-          <t>CANVA</t>
+          <t>ADOBE</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -17746,9 +18004,9 @@
         <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="n">
@@ -17764,35 +18022,35 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" ht="12" customHeight="1">
       <c r="C94" t="inlineStr">
         <is>
-          <t>GODADDY</t>
+          <t>CANVA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -17810,37 +18068,37 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" ht="12" customHeight="1">
       <c r="C95" t="inlineStr">
         <is>
-          <t>GOOGLEWORKSPACE</t>
+          <t>GODADDY</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
@@ -17856,13 +18114,13 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" ht="12" customHeight="1">
       <c r="C96" t="inlineStr">
         <is>
-          <t>GORGIAS</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -17886,10 +18144,10 @@
       <c r="J96" t="n">
         <v>1</v>
       </c>
-      <c r="K96" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
@@ -17902,13 +18160,13 @@
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" ht="12" customHeight="1">
       <c r="C97" t="inlineStr">
         <is>
-          <t>HETZNER</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -17932,10 +18190,10 @@
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
@@ -17948,40 +18206,40 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" ht="12" customHeight="1">
       <c r="C98" t="inlineStr">
         <is>
-          <t>KONVOAI</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
-      </c>
-      <c r="K98" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
@@ -17994,40 +18252,40 @@
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" ht="12" customHeight="1">
       <c r="C99" t="inlineStr">
         <is>
-          <t>MASMOVIL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
+        <v>2</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
@@ -18040,40 +18298,40 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" ht="12" customHeight="1">
       <c r="C100" t="inlineStr">
         <is>
-          <t>MICROSOFT</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
-      </c>
-      <c r="K100" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M100" t="n">
@@ -18086,40 +18344,40 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" ht="12" customHeight="1">
       <c r="C101" t="inlineStr">
         <is>
-          <t>OPENAI</t>
+          <t>MICROSOFT</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H101" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>3</v>
-      </c>
-      <c r="K101" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
+        <v>2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2</v>
+      </c>
+      <c r="L101" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
@@ -18132,40 +18390,40 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="12" customHeight="1">
       <c r="C102" t="inlineStr">
         <is>
-          <t>PRODUCTHERO</t>
+          <t>OPENAI</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
-      </c>
-      <c r="K102" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
+        <v>3</v>
+      </c>
+      <c r="K102" t="n">
+        <v>2</v>
+      </c>
+      <c r="L102" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
@@ -18178,13 +18436,13 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1">
       <c r="C103" t="inlineStr">
         <is>
-          <t>RAILWAY</t>
+          <t>PRODUCTHERO</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -18211,7 +18469,7 @@
       <c r="K103" t="n">
         <v>1</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
@@ -18230,35 +18488,35 @@
     <row r="104" ht="12" customHeight="1">
       <c r="C104" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>RAILWAY</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
-      </c>
-      <c r="K104" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -18270,40 +18528,40 @@
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1">
       <c r="C105" t="inlineStr">
         <is>
-          <t>SHOPIFY</t>
+          <t>REVER</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
@@ -18316,40 +18574,40 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1">
       <c r="C106" t="inlineStr">
         <is>
-          <t>SIMPLYCOM</t>
+          <t>SHOPIFY</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
+      <c r="K106" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="59" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
@@ -18362,37 +18620,37 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1">
       <c r="C107" t="inlineStr">
         <is>
-          <t>SYNCWITH</t>
+          <t>SIMPLYCOM</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" s="59" t="n">
+      <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="n">
@@ -18408,112 +18666,109 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1">
       <c r="C108" t="inlineStr">
         <is>
+          <t>SYNCWITH</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" ht="12" customHeight="1">
+      <c r="C109" t="inlineStr">
+        <is>
           <t>YUMAAI</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" t="n">
-        <v>1</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" t="n">
-        <v>1</v>
-      </c>
-      <c r="K108" s="59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" ht="12" customHeight="1">
-      <c r="A109" s="57" t="n"/>
-      <c r="B109" s="57" t="n"/>
-      <c r="C109" s="58" t="inlineStr">
-        <is>
-          <t>Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="D109" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="57" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q109" s="57" t="n"/>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="110" ht="12" customHeight="1">
       <c r="A110" s="57" t="n"/>
-      <c r="B110" s="58" t="inlineStr">
-        <is>
-          <t>Currency Adjustment</t>
-        </is>
-      </c>
-      <c r="C110" s="57" t="n"/>
+      <c r="B110" s="57" t="n"/>
+      <c r="C110" s="58" t="inlineStr">
+        <is>
+          <t>Uncategorized Expenses</t>
+        </is>
+      </c>
       <c r="D110" s="57" t="n">
         <v>1</v>
       </c>
@@ -18554,6 +18809,55 @@
         <v>4</v>
       </c>
       <c r="Q110" s="57" t="n"/>
+    </row>
+    <row r="111" ht="12" customHeight="1">
+      <c r="A111" s="57" t="n"/>
+      <c r="B111" s="58" t="inlineStr">
+        <is>
+          <t>Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="C111" s="57" t="n"/>
+      <c r="D111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q111" s="57" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -18950,23 +19254,23 @@
         <v>1160.58</v>
       </c>
       <c r="K8" s="50">
-        <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K115)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L8" s="50">
-        <f>('P&amp;G-SL'!L98+'P&amp;G-SL'!L114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L98+'P&amp;G-SL'!L115)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M8" s="50">
-        <f>('P&amp;G-SL'!M98+'P&amp;G-SL'!M114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M98+'P&amp;G-SL'!M115)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N8" s="50">
-        <f>('P&amp;G-SL'!N98+'P&amp;G-SL'!N114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N98+'P&amp;G-SL'!N115)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O8" s="50">
-        <f>('P&amp;G-SL'!O98+'P&amp;G-SL'!O114)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O98+'P&amp;G-SL'!O115)*VLOOKUP("pct_admin_uk",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P8" s="50">
@@ -19329,23 +19633,23 @@
         <v>773.72</v>
       </c>
       <c r="K16" s="50">
-        <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!K98+'P&amp;G-SL'!K115)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="L16" s="50">
-        <f>('P&amp;G-SL'!L98+'P&amp;G-SL'!L114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!L98+'P&amp;G-SL'!L115)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="M16" s="50">
-        <f>('P&amp;G-SL'!M98+'P&amp;G-SL'!M114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!M98+'P&amp;G-SL'!M115)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="N16" s="50">
-        <f>('P&amp;G-SL'!N98+'P&amp;G-SL'!N114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!N98+'P&amp;G-SL'!N115)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="O16" s="50">
-        <f>('P&amp;G-SL'!O98+'P&amp;G-SL'!O114)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
+        <f>('P&amp;G-SL'!O98+'P&amp;G-SL'!O115)*VLOOKUP("pct_admin_us",params!$A:$B,2,0)</f>
         <v/>
       </c>
       <c r="P16" s="50">
@@ -19616,7 +19920,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10T22:13:48Z</t>
+          <t>2026-09-04T07:59:27Z</t>
         </is>
       </c>
     </row>
@@ -19674,7 +19978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23334,7 +23638,7 @@
         </is>
       </c>
       <c r="E77" s="50" t="n">
-        <v>4336.431788617886</v>
+        <v>4336.451788617886</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -23350,7 +23654,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="50" t="n">
-        <v>4336.43</v>
+        <v>4336.45</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -23478,7 +23782,7 @@
         </is>
       </c>
       <c r="E80" s="50" t="n">
-        <v>2062.17</v>
+        <v>5384.02</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -23494,7 +23798,7 @@
         <v>1</v>
       </c>
       <c r="I80" s="50" t="n">
-        <v>2062.17</v>
+        <v>5384.02</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -23526,7 +23830,7 @@
         </is>
       </c>
       <c r="E81" s="50" t="n">
-        <v>2039.02</v>
+        <v>5783.04</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -23542,7 +23846,7 @@
         <v>1</v>
       </c>
       <c r="I81" s="50" t="n">
-        <v>2039.02</v>
+        <v>5783.04</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -23574,7 +23878,7 @@
         </is>
       </c>
       <c r="E82" s="50" t="n">
-        <v>792.85</v>
+        <v>2748.7</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -23590,7 +23894,7 @@
         <v>1</v>
       </c>
       <c r="I82" s="50" t="n">
-        <v>792.85</v>
+        <v>2748.7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -23622,7 +23926,7 @@
         </is>
       </c>
       <c r="E83" s="50" t="n">
-        <v>7854.36</v>
+        <v>24151.32</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -23638,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="I83" s="50" t="n">
-        <v>7854.36</v>
+        <v>24151.32</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -23670,7 +23974,7 @@
         </is>
       </c>
       <c r="E84" s="50" t="n">
-        <v>1737.85</v>
+        <v>3637.97</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -23686,7 +23990,7 @@
         <v>1</v>
       </c>
       <c r="I84" s="50" t="n">
-        <v>1737.85</v>
+        <v>3637.97</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -23718,7 +24022,7 @@
         </is>
       </c>
       <c r="E85" s="50" t="n">
-        <v>19060.68</v>
+        <v>65408.07</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -23734,7 +24038,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="50" t="n">
-        <v>19060.68</v>
+        <v>65408.07</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -23766,7 +24070,7 @@
         </is>
       </c>
       <c r="E86" s="50" t="n">
-        <v>10662.8</v>
+        <v>31071.53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -23782,7 +24086,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="50" t="n">
-        <v>10662.8</v>
+        <v>31071.53</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -23805,16 +24109,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="E87" s="50" t="n">
-        <v>7020.86</v>
+        <v>122.02</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -23830,7 +24134,7 @@
         <v>1</v>
       </c>
       <c r="I87" s="50" t="n">
-        <v>7020.86</v>
+        <v>122.02</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -23853,16 +24157,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E88" s="50" t="n">
-        <v>1938.9</v>
+        <v>16806.38</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -23878,7 +24182,7 @@
         <v>1</v>
       </c>
       <c r="I88" s="50" t="n">
-        <v>1938.9</v>
+        <v>16806.38</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -23901,16 +24205,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E89" s="50" t="n">
-        <v>2595.85</v>
+        <v>111.84</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -23926,7 +24230,7 @@
         <v>1</v>
       </c>
       <c r="I89" s="50" t="n">
-        <v>2595.85</v>
+        <v>111.84</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -23949,16 +24253,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E90" s="50" t="n">
-        <v>1338</v>
+        <v>6489.92</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -23974,7 +24278,7 @@
         <v>1</v>
       </c>
       <c r="I90" s="50" t="n">
-        <v>1338</v>
+        <v>6489.92</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -23997,16 +24301,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E91" s="50" t="n">
-        <v>1606.98</v>
+        <v>7739.27</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -24022,7 +24326,7 @@
         <v>1</v>
       </c>
       <c r="I91" s="50" t="n">
-        <v>1606.98</v>
+        <v>7739.27</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -24031,6 +24335,726 @@
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92" ht="12" customHeight="1">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E92" s="50" t="n">
+        <v>4126.93</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H92" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="50" t="n">
+        <v>4126.93</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93" ht="12" customHeight="1">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E93" s="50" t="n">
+        <v>4367.09</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H93" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="50" t="n">
+        <v>4367.09</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94" ht="12" customHeight="1">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="E94" s="50" t="n">
+        <v>305.59</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H94" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="50" t="n">
+        <v>305.59</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95" ht="12" customHeight="1">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E95" s="50" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H95" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="50" t="n">
+        <v>379.38</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96" ht="12" customHeight="1">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="E96" s="50" t="n">
+        <v>248.15</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H96" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="50" t="n">
+        <v>248.15</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+    </row>
+    <row r="97" ht="12" customHeight="1">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E97" s="50" t="n">
+        <v>1796.77</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H97" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="50" t="n">
+        <v>1796.77</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+    </row>
+    <row r="98" ht="12" customHeight="1">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E98" s="50" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H98" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="50" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99" ht="12" customHeight="1">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="E99" s="50" t="n">
+        <v>7567.43</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H99" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="50" t="n">
+        <v>7567.43</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+    </row>
+    <row r="100" ht="12" customHeight="1">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E100" s="50" t="n">
+        <v>4375.88</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H100" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="50" t="n">
+        <v>4375.88</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+    </row>
+    <row r="101" ht="12" customHeight="1">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E101" s="50" t="n">
+        <v>1985.8</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H101" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="50" t="n">
+        <v>1985.8</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+    </row>
+    <row r="102" ht="12" customHeight="1">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E102" s="50" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H102" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="50" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+    </row>
+    <row r="103" ht="12" customHeight="1">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E103" s="50" t="n">
+        <v>1084.32</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H103" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="50" t="n">
+        <v>1084.32</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+    </row>
+    <row r="104" ht="12" customHeight="1">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E104" s="50" t="n">
+        <v>705.03</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H104" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="50" t="n">
+        <v>705.03</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+    </row>
+    <row r="105" ht="12" customHeight="1">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E105" s="50" t="n">
+        <v>492</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H105" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="50" t="n">
+        <v>492</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+    </row>
+    <row r="106" ht="12" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E106" s="50" t="n">
+        <v>749.39</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H106" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="50" t="n">
+        <v>749.39</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>finance.informe_vat_gestorias_detalle</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27909,7 +28933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N420"/>
+  <dimension ref="A1:N459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -51750,10 +52774,10 @@
         </is>
       </c>
       <c r="J380" s="51" t="n">
-        <v>0.86542622</v>
+        <v>0.86236633</v>
       </c>
       <c r="K380" s="50" t="n">
-        <v>92.19</v>
+        <v>91.86</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -53024,22 +54048,22 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>technology</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>REVER</t>
+          <t>CORREOS</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" s="50" t="n">
-        <v>111.07</v>
+        <v>91.64</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -53055,7 +54079,7 @@
         <v>1</v>
       </c>
       <c r="K401" s="50" t="n">
-        <v>111.07</v>
+        <v>91.64</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -53064,12 +54088,12 @@
       </c>
       <c r="M401" s="52" t="inlineStr">
         <is>
-          <t>RVR-22464</t>
+          <t>4004777304</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1au7VshI0RM4MtoRue5AClrxY4yPL64dH/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/10mv-XY9xivw6xwGVxgPpKLx1bzcFXLfv/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
@@ -53086,22 +54110,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>cogs</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>TORRAS</t>
+          <t>CORREOSCAN</t>
         </is>
       </c>
       <c r="F402" t="inlineStr"/>
       <c r="G402" s="50" t="n">
-        <v>15</v>
+        <v>23.69</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -53117,7 +54141,7 @@
         <v>1</v>
       </c>
       <c r="K402" s="50" t="n">
-        <v>15</v>
+        <v>23.69</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -53126,19 +54150,19 @@
       </c>
       <c r="M402" s="52" t="inlineStr">
         <is>
-          <t>7/3096</t>
+          <t>4004777306</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1HJkenN15mK2054HGwv4o35gMpC0wDJ58/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/17htRuHJIEKYNLRJmez50JvcjVaZvG0Cs/view?usp=drivesdk</t>
         </is>
       </c>
     </row>
     <row r="403" ht="12" customHeight="1">
       <c r="A403" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -53153,17 +54177,17 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" s="50" t="n">
-        <v>13737</v>
+        <v>6510.57</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -53179,20 +54203,28 @@
         <v>1</v>
       </c>
       <c r="K403" s="50" t="n">
-        <v>13737</v>
+        <v>6510.57</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M403" s="52" t="inlineStr">
+        <is>
+          <t>26-1485</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1S9T24h6VHO0aMJOEreoLD4UVmXLiiUKU/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="12" customHeight="1">
       <c r="A404" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -53207,17 +54239,17 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>DCT</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
       <c r="G404" s="50" t="n">
-        <v>16662</v>
+        <v>4653.52</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
@@ -53233,20 +54265,28 @@
         <v>1</v>
       </c>
       <c r="K404" s="50" t="n">
-        <v>16662</v>
+        <v>4653.52</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M404" t="inlineStr"/>
-      <c r="N404" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M404" s="52" t="inlineStr">
+        <is>
+          <t>26-1560</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/12_h_Rnf6rHfnetSYyinGf6aSha9KtwW3/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="12" customHeight="1">
       <c r="A405" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -53256,22 +54296,26 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
       <c r="G405" s="50" t="n">
-        <v>14544</v>
+        <v>32360.86</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -53287,20 +54331,28 @@
         <v>1</v>
       </c>
       <c r="K405" s="50" t="n">
-        <v>14544</v>
+        <v>32360.86</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M405" t="inlineStr"/>
-      <c r="N405" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M405" s="52" t="inlineStr">
+        <is>
+          <t>5685041161</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1PIHw8IUt4wwlaHPnm54dRIWHq501o6CI/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="12" customHeight="1">
       <c r="A406" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -53310,22 +54362,26 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>uk</t>
+        </is>
+      </c>
       <c r="G406" s="50" t="n">
-        <v>13605</v>
+        <v>5369.38</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -53341,20 +54397,28 @@
         <v>1</v>
       </c>
       <c r="K406" s="50" t="n">
-        <v>13605</v>
+        <v>5369.38</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr"/>
-      <c r="N406" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M406" s="52" t="inlineStr">
+        <is>
+          <t>5685041161</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1PIHw8IUt4wwlaHPnm54dRIWHq501o6CI/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="12" customHeight="1">
       <c r="A407" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -53364,22 +54428,26 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr"/>
+          <t>GOOGLEADS</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="G407" s="50" t="n">
-        <v>13698</v>
+        <v>1509.47</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -53395,20 +54463,28 @@
         <v>1</v>
       </c>
       <c r="K407" s="50" t="n">
-        <v>13698</v>
+        <v>1509.47</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M407" s="52" t="inlineStr">
+        <is>
+          <t>5685041161</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1PIHw8IUt4wwlaHPnm54dRIWHq501o6CI/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="12" customHeight="1">
       <c r="A408" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -53418,22 +54494,22 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>GOOGLEWORKSPACE</t>
         </is>
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" s="50" t="n">
-        <v>11562</v>
+        <v>210.6</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -53449,20 +54525,28 @@
         <v>1</v>
       </c>
       <c r="K408" s="50" t="n">
-        <v>11562</v>
+        <v>210.6</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M408" t="inlineStr"/>
-      <c r="N408" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M408" s="52" t="inlineStr">
+        <is>
+          <t>5665849320</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1hPrQRj-4k-uKXyyyV5K5c77230v3yNAE/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="12" customHeight="1">
       <c r="A409" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -53472,26 +54556,26 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>cogs</t>
+          <t>opex</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>royalties</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>ROYALTIES</t>
+          <t>GORGIAS</t>
         </is>
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" s="50" t="n">
-        <v>14826</v>
+        <v>120</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -53500,23 +54584,31 @@
         </is>
       </c>
       <c r="J409" s="51" t="n">
-        <v>1</v>
+        <v>0.86236633</v>
       </c>
       <c r="K409" s="50" t="n">
-        <v>14826</v>
+        <v>103.48</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>artist_royalties_monthly_summary</t>
-        </is>
-      </c>
-      <c r="M409" t="inlineStr"/>
-      <c r="N409" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M409" s="52" t="inlineStr">
+        <is>
+          <t>INC-08-2026-144671</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/10UbrnfiWuFBFSYYNGKnakLt-FLu6pi3H/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="12" customHeight="1">
       <c r="A410" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -53531,17 +54623,21 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
       <c r="G410" s="50" t="n">
-        <v>14731.84</v>
+        <v>2593.09</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -53557,20 +54653,28 @@
         <v>1</v>
       </c>
       <c r="K410" s="50" t="n">
-        <v>14731.84</v>
+        <v>2593.09</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M410" t="inlineStr"/>
-      <c r="N410" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M410" s="52" t="inlineStr">
+        <is>
+          <t>VTA/26-029666</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Gj6EIhz69krZpU8fJNG9EZZVQudieR75/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="12" customHeight="1">
       <c r="A411" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -53585,17 +54689,21 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr"/>
+          <t>HANNUN</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
       <c r="G411" s="50" t="n">
-        <v>14915.68</v>
+        <v>175</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -53611,20 +54719,28 @@
         <v>1</v>
       </c>
       <c r="K411" s="50" t="n">
-        <v>14915.68</v>
+        <v>175</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr"/>
-      <c r="N411" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M411" s="52" t="inlineStr">
+        <is>
+          <t>VTA/26-029570</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/18iFi40prz4PZgymSEHZ35LeanirV-3tM/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="12" customHeight="1">
       <c r="A412" t="inlineStr">
         <is>
-          <t>202603</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -53639,17 +54755,17 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>HETZNER</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" s="50" t="n">
-        <v>15349.42</v>
+        <v>10.9</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
@@ -53665,20 +54781,28 @@
         <v>1</v>
       </c>
       <c r="K412" s="50" t="n">
-        <v>15349.42</v>
+        <v>10.9</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M412" s="52" t="inlineStr">
+        <is>
+          <t>080001112398</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1UIzwBHEGytfpmZd6TnrQ4N1mNywQY7AM/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="12" customHeight="1">
       <c r="A413" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -53693,17 +54817,17 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" s="50" t="n">
-        <v>15515.1</v>
+        <v>926.9299999999999</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -53719,20 +54843,28 @@
         <v>1</v>
       </c>
       <c r="K413" s="50" t="n">
-        <v>15515.1</v>
+        <v>926.9299999999999</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M413" s="52" t="inlineStr">
+        <is>
+          <t>B5F7DF3C-9124</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1MPlVmbLRKdYIx7_brPM4w4styEspyjtS/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="12" customHeight="1">
       <c r="A414" t="inlineStr">
         <is>
-          <t>202605</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -53747,17 +54879,17 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>KONVOAI</t>
         </is>
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" s="50" t="n">
-        <v>15515.1</v>
+        <v>429</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -53773,20 +54905,28 @@
         <v>1</v>
       </c>
       <c r="K414" s="50" t="n">
-        <v>15515.1</v>
+        <v>429</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M414" s="52" t="inlineStr">
+        <is>
+          <t>B5F7DF3C-9306</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1Z8tqHNSRPPN6RTCpn4_Rml38rc4sjq6q/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="12" customHeight="1">
       <c r="A415" t="inlineStr">
         <is>
-          <t>202606</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -53801,17 +54941,17 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
+          <t>MASMOVIL</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" s="50" t="n">
-        <v>15421.77</v>
+        <v>10</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
@@ -53827,20 +54967,28 @@
         <v>1</v>
       </c>
       <c r="K415" s="50" t="n">
-        <v>15421.77</v>
+        <v>10</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M415" s="52" t="inlineStr">
+        <is>
+          <t>MC260010103548</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/17st8j7Yufq7w9pMBLubY8EMendDclUEW/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="12" customHeight="1">
       <c r="A416" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -53855,17 +55003,21 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>PAYROLL</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr"/>
+          <t>METAADS</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>eu</t>
+        </is>
+      </c>
       <c r="G416" s="50" t="n">
-        <v>15515.1</v>
+        <v>26816.39</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
@@ -53881,20 +55033,28 @@
         <v>1</v>
       </c>
       <c r="K416" s="50" t="n">
-        <v>15515.1</v>
+        <v>26816.39</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>payroll_documents</t>
-        </is>
-      </c>
-      <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M416" s="52" t="inlineStr">
+        <is>
+          <t>255139222</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1GpQi2PaH0qJ7OboBoSyneDOEvIriXM7A/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="12" customHeight="1">
       <c r="A417" t="inlineStr">
         <is>
-          <t>202601</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -53909,21 +55069,21 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Otros gastos enero 2026</t>
+          <t>uk</t>
         </is>
       </c>
       <c r="G417" s="50" t="n">
-        <v>411.87</v>
+        <v>3726.05</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
@@ -53939,20 +55099,28 @@
         <v>1</v>
       </c>
       <c r="K417" s="50" t="n">
-        <v>411.87</v>
+        <v>3726.05</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M417" s="52" t="inlineStr">
+        <is>
+          <t>255139222</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1GpQi2PaH0qJ7OboBoSyneDOEvIriXM7A/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="12" customHeight="1">
       <c r="A418" t="inlineStr">
         <is>
-          <t>202602</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -53967,21 +55135,21 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
+          <t>METAADS</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Otros gastos febrero 2026</t>
+          <t>us</t>
         </is>
       </c>
       <c r="G418" s="50" t="n">
-        <v>554.46</v>
+        <v>903.9</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
@@ -53997,20 +55165,28 @@
         <v>1</v>
       </c>
       <c r="K418" s="50" t="n">
-        <v>554.46</v>
+        <v>903.9</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M418" s="52" t="inlineStr">
+        <is>
+          <t>255139222</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1GpQi2PaH0qJ7OboBoSyneDOEvIriXM7A/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="12" customHeight="1">
       <c r="A419" t="inlineStr">
         <is>
-          <t>202604</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -54025,21 +55201,17 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>OTROSGASTOS</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>Gastos no categorizados abril 2026</t>
-        </is>
-      </c>
+          <t>MICROSOFT</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
       <c r="G419" s="50" t="n">
-        <v>935.45</v>
+        <v>30.87</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
@@ -54055,73 +55227,2363 @@
         <v>1</v>
       </c>
       <c r="K419" s="50" t="n">
-        <v>935.45</v>
+        <v>30.87</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>otros_gastos</t>
-        </is>
-      </c>
-      <c r="M419" t="inlineStr"/>
-      <c r="N419" t="inlineStr"/>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M419" s="52" t="inlineStr">
+        <is>
+          <t>G177857024</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1jKx9K_pR2FSRuK3vX34x07mR7n7VdrBT/view?usp=drivesdk</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="12" customHeight="1">
       <c r="A420" t="inlineStr">
         <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>MICROSOFT</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" s="50" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J420" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K420" s="50" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M420" s="52" t="inlineStr">
+        <is>
+          <t>G178635168</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/15Tz2LINii2mtIaELwF2fWmlQCPjuVnyO/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="12" customHeight="1">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" s="50" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J421" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K421" s="50" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M421" s="52" t="inlineStr">
+        <is>
+          <t>7BSDV5AM-0005</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1aXHZSnItkK3xl0G5wvLNORbHdHf0JDWr/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="12" customHeight="1">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>OPENAI</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>api_usage</t>
+        </is>
+      </c>
+      <c r="G422" s="50" t="n">
+        <v>100</v>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J422" s="51" t="n">
+        <v>0.86236633</v>
+      </c>
+      <c r="K422" s="50" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M422" s="52" t="inlineStr">
+        <is>
+          <t>1D95DDC4-0022</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1-PEvZQohMLSVNQHAH7cLTBQWOVGX4QX3/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="12" customHeight="1">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>manufacturing</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>PRESSING</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" s="50" t="n">
+        <v>34048.26</v>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J423" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K423" s="50" t="n">
+        <v>34048.26</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M423" s="52" t="inlineStr">
+        <is>
+          <t>FAC/2026/26100007500</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1IOgR9GpK9ad1id19cCHFI72ivJwQU1lL/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="12" customHeight="1">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>PRODUCTHERO</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" s="50" t="n">
+        <v>267</v>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J424" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K424" s="50" t="n">
+        <v>267</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M424" s="52" t="inlineStr">
+        <is>
+          <t>246556</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1RQAPQId4qHh-F50y99Vz3qTyz_UYpc0s/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="12" customHeight="1">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>RAILWAY</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" s="50" t="n">
+        <v>123.52</v>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J425" s="51" t="n">
+        <v>0.86095566</v>
+      </c>
+      <c r="K425" s="50" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M425" s="52" t="inlineStr">
+        <is>
+          <t>1602C2F5-0026</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1D8qTVCwb8i3ZJ1K4uwN5QHYxQyzoOlxb/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="12" customHeight="1">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" s="50" t="n">
+        <v>111.07</v>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J426" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K426" s="50" t="n">
+        <v>111.07</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M426" s="52" t="inlineStr">
+        <is>
+          <t>RVR-22464</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1au7VshI0RM4MtoRue5AClrxY4yPL64dH/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="12" customHeight="1">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>REVER</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" s="50" t="n">
+        <v>79</v>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J427" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K427" s="50" t="n">
+        <v>79</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M427" s="52" t="inlineStr">
+        <is>
+          <t>RVR-23258</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1TlUEj1tCc4NprZ8HmK3Hi-AfOrtIPGqa/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="12" customHeight="1">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>SHOPIFY</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" s="50" t="n">
+        <v>3395.09</v>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J428" s="51" t="n">
+        <v>0.86236633</v>
+      </c>
+      <c r="K428" s="50" t="n">
+        <v>2927.81</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M428" s="52" t="inlineStr">
+        <is>
+          <t>578757141</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1_N1aboySOmUmy0rXwjlJhrO2RjBskqZ3/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="12" customHeight="1">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J429" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K429" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M429" s="52" t="inlineStr">
+        <is>
+          <t>7/3096</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HJkenN15mK2054HGwv4o35gMpC0wDJ58/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="12" customHeight="1">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" s="50" t="n">
+        <v>1414.75</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J430" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K430" s="50" t="n">
+        <v>1414.75</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M430" s="52" t="inlineStr">
+        <is>
+          <t>328001107</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1kU_P6CrJDnHAs5wAhprpDT-yK1QELQhC/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="12" customHeight="1">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" s="50" t="n">
+        <v>1649.66</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J431" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K431" s="50" t="n">
+        <v>1649.66</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M431" s="52" t="inlineStr">
+        <is>
+          <t>328032197</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/10YYpHK3NVq4kaonUrKiEvNk9JygNiheF/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="12" customHeight="1">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" s="50" t="n">
+        <v>2526.18</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J432" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K432" s="50" t="n">
+        <v>2526.18</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M432" s="52" t="inlineStr">
+        <is>
+          <t>328063022</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1HvM2rBFSAkQzyAJd-BGOMTAhuaQwOL6M/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="12" customHeight="1">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" s="50" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J433" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K433" s="50" t="n">
+        <v>47.47</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M433" s="52" t="inlineStr">
+        <is>
+          <t>839031074</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1eTuIHUYWYpd8FWBTEZS1ut1u-D-c9eqC/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="12" customHeight="1">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" s="50" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J434" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K434" s="50" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M434" s="52" t="inlineStr">
+        <is>
+          <t>839074010</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1kNjOGookgIVL9pEc0JqApL59oAJk31y2/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="12" customHeight="1">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" s="50" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J435" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K435" s="50" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M435" s="52" t="inlineStr">
+        <is>
+          <t>839110446</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1NmOjrHUO7AM_-vS_b2FlQV-peec_FPkI/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="12" customHeight="1">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" s="50" t="n">
+        <v>120.87</v>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J436" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K436" s="50" t="n">
+        <v>120.87</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M436" s="52" t="inlineStr">
+        <is>
+          <t>839147396</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1donXbz2anRarfy6DkcjvpLrF_FKSIfOK/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="12" customHeight="1">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>YUMAAI</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" s="50" t="n">
+        <v>440</v>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J437" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K437" s="50" t="n">
+        <v>440</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M437" s="52" t="inlineStr">
+        <is>
+          <t>OQXBYXMP-0011</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1fNLDGZXqoNUpvRv49sTX2FNtTvjivN87/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="12" customHeight="1">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" s="50" t="n">
+        <v>95</v>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J438" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K438" s="50" t="n">
+        <v>95</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M438" s="52" t="inlineStr">
+        <is>
+          <t>F260634</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1uqaXfc7rjA37wvDkIob331fuoG3yCWDq/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="12" customHeight="1">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>TORRAS</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J439" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K439" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>documents</t>
+        </is>
+      </c>
+      <c r="M439" s="52" t="inlineStr">
+        <is>
+          <t>7/3331</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1aigavoVpf1L4hcM5SF4KCkSPcTt2Futn/view?usp=drivesdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="440" ht="12" customHeight="1">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" s="50" t="n">
+        <v>13737</v>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J440" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" s="50" t="n">
+        <v>13737</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
+    </row>
+    <row r="441" ht="12" customHeight="1">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" s="50" t="n">
+        <v>16662</v>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J441" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K441" s="50" t="n">
+        <v>16662</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
+    </row>
+    <row r="442" ht="12" customHeight="1">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" s="50" t="n">
+        <v>14544</v>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J442" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K442" s="50" t="n">
+        <v>14544</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+    </row>
+    <row r="443" ht="12" customHeight="1">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" s="50" t="n">
+        <v>13605</v>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J443" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K443" s="50" t="n">
+        <v>13605</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+    </row>
+    <row r="444" ht="12" customHeight="1">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" s="50" t="n">
+        <v>13698</v>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J444" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K444" s="50" t="n">
+        <v>13698</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
+    </row>
+    <row r="445" ht="12" customHeight="1">
+      <c r="A445" t="inlineStr">
+        <is>
           <t>202606</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" s="50" t="n">
+        <v>11562</v>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J445" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K445" s="50" t="n">
+        <v>11562</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
+    </row>
+    <row r="446" ht="12" customHeight="1">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" s="50" t="n">
+        <v>14826</v>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J446" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K446" s="50" t="n">
+        <v>14826</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
+    </row>
+    <row r="447" ht="12" customHeight="1">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>royalties</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>ROYALTIES</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" s="50" t="n">
+        <v>17256</v>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J447" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" s="50" t="n">
+        <v>17256</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>artist_royalties_monthly_summary</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
+    </row>
+    <row r="448" ht="12" customHeight="1">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
         <is>
           <t>opex</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" s="50" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J448" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K448" s="50" t="n">
+        <v>14731.84</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
+    </row>
+    <row r="449" ht="12" customHeight="1">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" s="50" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J449" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K449" s="50" t="n">
+        <v>14915.68</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
+    </row>
+    <row r="450" ht="12" customHeight="1">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>202603</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" s="50" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J450" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K450" s="50" t="n">
+        <v>15349.42</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr"/>
+    </row>
+    <row r="451" ht="12" customHeight="1">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J451" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K451" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
+    </row>
+    <row r="452" ht="12" customHeight="1">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>202605</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J452" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K452" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
+    </row>
+    <row r="453" ht="12" customHeight="1">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" s="50" t="n">
+        <v>15421.77</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J453" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K453" s="50" t="n">
+        <v>15421.77</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr"/>
+    </row>
+    <row r="454" ht="12" customHeight="1">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J454" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K454" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
+    </row>
+    <row r="455" ht="12" customHeight="1">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>staff</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>PAYROLL</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J455" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K455" s="50" t="n">
+        <v>15515.1</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>payroll_documents</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
+    </row>
+    <row r="456" ht="12" customHeight="1">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>202601</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
+      <c r="E456" t="inlineStr">
         <is>
           <t>OTROSGASTOS</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr">
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Otros gastos enero 2026</t>
+        </is>
+      </c>
+      <c r="G456" s="50" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J456" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K456" s="50" t="n">
+        <v>411.87</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
+    </row>
+    <row r="457" ht="12" customHeight="1">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>202602</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Otros gastos febrero 2026</t>
+        </is>
+      </c>
+      <c r="G457" s="50" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J457" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K457" s="50" t="n">
+        <v>554.46</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
+    </row>
+    <row r="458" ht="12" customHeight="1">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>202604</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Gastos no categorizados abril 2026</t>
+        </is>
+      </c>
+      <c r="G458" s="50" t="n">
+        <v>935.45</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J458" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K458" s="50" t="n">
+        <v>935.45</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
+    </row>
+    <row r="459" ht="12" customHeight="1">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>202606</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>opex</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>otros_gastos</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>OTROSGASTOS</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
         <is>
           <t>Otros gastos junio 2026</t>
         </is>
       </c>
-      <c r="G420" s="50" t="n">
+      <c r="G459" s="50" t="n">
         <v>240.24</v>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="J420" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K420" s="50" t="n">
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="J459" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K459" s="50" t="n">
         <v>240.24</v>
       </c>
-      <c r="L420" t="inlineStr">
+      <c r="L459" t="inlineStr">
         <is>
           <t>otros_gastos</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr"/>
-      <c r="N420" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -54526,6 +57988,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M400" r:id="rId398"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M401" r:id="rId399"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M402" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M403" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M404" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M405" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M406" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M407" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M408" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M409" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M410" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M411" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M412" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M413" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M414" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M415" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M416" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M417" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M418" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M419" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M420" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M421" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M422" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M423" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M424" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M425" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M426" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M427" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M428" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M429" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M430" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M431" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M432" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M433" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M434" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M435" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M436" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M437" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M438" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M439" r:id="rId437"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
